--- a/workspaces/btc_daily_14days/cycle/cycle_phase.xlsx
+++ b/workspaces/btc_daily_14days/cycle/cycle_phase.xlsx
@@ -575,46 +575,46 @@
         <v>143</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.640291467063122</v>
+        <v>-5.621626794213384</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.554195988585676</v>
+        <v>-6.532985086416502</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.44923052420802</v>
+        <v>-10.41481991172969</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.92020532373565</v>
+        <v>-15.86770145192116</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.36317858438493</v>
+        <v>-14.31582471421817</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-18.27001143145282</v>
+        <v>-18.21010480397251</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-16.95895467608668</v>
+        <v>-16.90294214693365</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-16.73067372507044</v>
+        <v>-16.67553833671896</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.79634530689784</v>
+        <v>-16.74051033666773</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-15.5499624456874</v>
+        <v>-15.49831773085697</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-12.95513509633809</v>
+        <v>-12.91174609239396</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-15.72892001638123</v>
+        <v>-15.67651649984892</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-13.3486757175037</v>
+        <v>-13.30420994935406</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.787133218778926</v>
+        <v>-6.764202767074636</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>142</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.548815200916785</v>
+        <v>4.534214841081649</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.346791186394633</v>
+        <v>4.332505561573335</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.657265258578207</v>
+        <v>4.642859172830676</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.017208522940564</v>
+        <v>8.988806383101576</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.1201887800944</v>
+        <v>14.07419154541006</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.89574692254573</v>
+        <v>10.86091742502042</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12.92943417747281</v>
+        <v>12.88796227850231</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.75916164506616</v>
+        <v>11.72150418304309</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.28920579752404</v>
+        <v>10.25707656109713</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.96917190213077</v>
+        <v>12.92766381664815</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.942826784305282</v>
+        <v>9.911567007945322</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.979506820425769</v>
+        <v>9.948374348818959</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.854289028030031</v>
+        <v>8.826550244173937</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.28131408538821</v>
+        <v>6.261503920603573</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>143</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.646421819650158</v>
+        <v>7.619744811650541</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.435473171109791</v>
+        <v>7.409166815417422</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.24035184338209</v>
+        <v>11.20156797561751</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.37362182142345</v>
+        <v>11.33469291269761</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.93808324452819</v>
+        <v>12.89269980709213</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.53892723862889</v>
+        <v>12.49559332389725</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>15.25915257168746</v>
+        <v>15.20623576096668</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.79517051070956</v>
+        <v>14.74386790274227</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>18.94247039397418</v>
+        <v>18.87727530483348</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>20.19877563249106</v>
+        <v>20.12850574954851</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>20.69982228310606</v>
+        <v>20.62813033013646</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.44101128287865</v>
+        <v>21.36696706557517</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23.13015894227109</v>
+        <v>23.04982655627104</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>26.19464000223894</v>
+        <v>26.10293010005775</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>142</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.774167313592685</v>
+        <v>8.741195807798185</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.277977298018619</v>
+        <v>9.242779264344257</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.1132597307646</v>
+        <v>13.06446704059424</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>16.06659563708229</v>
+        <v>16.00728126084461</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13.41744185957673</v>
+        <v>13.36663972220686</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>15.83459713020071</v>
+        <v>15.77565850122242</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>15.04900395232904</v>
+        <v>14.9925956632352</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>16.70208632305714</v>
+        <v>16.6396411793725</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>18.76308524996262</v>
+        <v>18.6932962695203</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>21.44688391804257</v>
+        <v>21.3663645795298</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>26.19108036207126</v>
+        <v>26.09342896278456</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>28.35221798966907</v>
+        <v>28.2468058647827</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>31.47232575904231</v>
+        <v>31.35485938982865</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>30.31942584780023</v>
+        <v>30.20516589243439</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>143</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.947121120349784</v>
+        <v>6.918379055144527</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.337321339904733</v>
+        <v>5.314261517149006</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.944001766819362</v>
+        <v>4.922402487619195</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.57565142069982</v>
+        <v>8.540048793897746</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.439871871399177</v>
+        <v>9.400039032997114</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.639654996358061</v>
+        <v>7.607156184257448</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.455781258196659</v>
+        <v>5.431381081251509</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.391119447407277</v>
+        <v>6.362924658299733</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.22933153536065</v>
+        <v>4.209350727830532</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.678265393656602</v>
+        <v>2.662873936504965</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.578503886378158</v>
+        <v>4.555434940063705</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.018042454895529</v>
+        <v>5.98932503429905</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.301328912669447</v>
+        <v>6.27041087691984</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>9.363299863096188</v>
+        <v>9.319713316841131</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>142</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.436139144578441</v>
+        <v>2.422911002221284</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.39173685301393</v>
+        <v>11.3424533367914</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.591098580981892</v>
+        <v>9.549029420737156</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.13462694473838</v>
+        <v>11.08567455457483</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.48438808761739</v>
+        <v>8.444883948552437</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.19565047497373</v>
+        <v>10.15008582564309</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.703181271520457</v>
+        <v>8.663661091314921</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.943990570379817</v>
+        <v>8.903119631365847</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.650039567583207</v>
+        <v>4.626625877345511</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.800200409785027</v>
+        <v>3.778975090242142</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.184240010604299</v>
+        <v>2.168720504845062</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.220267897681957</v>
+        <v>2.204215484580452</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.800864496382005</v>
+        <v>1.785227640590179</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.06681510958549097</v>
+        <v>-0.07652424841051442</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>142</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.027688440353565</v>
+        <v>1.019139740673246</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.529757060248691</v>
+        <v>1.517196765472313</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.477654425088154</v>
+        <v>7.44057791195555</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.086606286107539</v>
+        <v>4.062644825126092</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.664970403688606</v>
+        <v>5.633644159928132</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.849019059856431</v>
+        <v>3.825822850393017</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.765743857901803</v>
+        <v>3.74325356682801</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.299492777659033</v>
+        <v>3.2784839365954</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.769483322529304</v>
+        <v>6.735072122053289</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.626623049142225</v>
+        <v>6.591644840511968</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.424315973677295</v>
+        <v>6.389655462401372</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.341687727807809</v>
+        <v>4.315301763866174</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.216093983802345</v>
+        <v>3.193113446216167</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.06592476556651405</v>
+        <v>-0.07652424841051442</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>144</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.104549431321246</v>
+        <v>-1.10457683490457</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.105852662667012</v>
+        <v>-4.094923179260249</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.501704325805328</v>
+        <v>-4.489850366582957</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.286677753481939</v>
+        <v>-2.285015574991256</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.737460355883869</v>
+        <v>2.715944740884723</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4413908746315087</v>
+        <v>-0.4480189070071745</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.736694303631708</v>
+        <v>5.703396669657458</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.790763089031323</v>
+        <v>1.774341219447287</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.426870108027835</v>
+        <v>2.408174473448767</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.576466482068085</v>
+        <v>1.560250332676894</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.463068789983055</v>
+        <v>3.438045266962206</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.499559334877851</v>
+        <v>3.474320128663976</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.686127838732411</v>
+        <v>1.667637229040963</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.939190903063391</v>
+        <v>1.918780915908734</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>141</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.407270899648346</v>
+        <v>1.395681912233592</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5056239795014648</v>
+        <v>0.4964351288991367</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1113066181805209</v>
+        <v>0.1031284485909865</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.922355716698753</v>
+        <v>5.886409500767016</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4150999827897692</v>
+        <v>0.4021007340116824</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.8448244599563</v>
+        <v>2.822405351978112</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.762068772864481</v>
+        <v>2.739100450825383</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.717232503847193</v>
+        <v>3.690288745688157</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.636513967359761</v>
+        <v>8.587356872241024</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>7.788287290333152</v>
+        <v>7.741849805336862</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.298913615519183</v>
+        <v>8.249112150270605</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9.761320524614064</v>
+        <v>9.70471987796239</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>10.05673968351332</v>
+        <v>9.997864019753159</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.31311818364873</v>
+        <v>10.25211424924206</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>143</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.444487271258922</v>
+        <v>-1.443480589846097</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.657484331521779</v>
+        <v>-1.657161334819648</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.146384996296163</v>
+        <v>2.127476543679556</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5215078849268124</v>
+        <v>-0.5300262479513549</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.741709768087439</v>
+        <v>1.720903765446138</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5.543820846203033</v>
+        <v>5.505945369959576</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.864020954329888</v>
+        <v>6.818737799398754</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.502373382519004</v>
+        <v>8.449382324307841</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.042938839340806</v>
+        <v>6.996300708297468</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.089351958262355</v>
+        <v>4.055926372438066</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.483538850360105</v>
+        <v>2.456651723596266</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.733590096892769</v>
+        <v>6.68567174401857</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.721041642297003</v>
+        <v>7.667252997935769</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.977253389951514</v>
+        <v>7.921111918239731</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>143</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5.548519721748221</v>
+        <v>5.513834721386786</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6.037851415066697</v>
+        <v>5.998809706117676</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.045676797867152</v>
+        <v>6.999553453218638</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.580377128392456</v>
+        <v>8.524296434923428</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.244452689529531</v>
+        <v>5.203368555839205</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.742742866838093</v>
+        <v>2.714942864216844</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.062552132519436</v>
+        <v>4.026512030905359</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.194490421715237</v>
+        <v>2.167827459542671</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7325824708471984</v>
+        <v>0.7130007113328674</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.986602882934683</v>
+        <v>1.960178486725148</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3796803060007008</v>
+        <v>0.3605365596317824</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2852582076360903</v>
+        <v>-0.3026368287120462</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.7047967052224635</v>
+        <v>-0.721502897346582</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.262784277301392</v>
+        <v>-3.267699270571455</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>141</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.394147540068289</v>
+        <v>-6.368196954816035</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-12.26531409706267</v>
+        <v>-12.20975476084194</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-11.24478777747364</v>
+        <v>-11.19721762354018</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-16.0881421235345</v>
+        <v>-16.01713197741618</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-18.05333973383728</v>
+        <v>-17.97298791776321</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-20.60477620496739</v>
+        <v>-20.50929741393178</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-22.11812944040587</v>
+        <v>-22.01650754385904</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-26.86249248549989</v>
+        <v>-26.73478993618928</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-31.20311225284352</v>
+        <v>-31.05188383233067</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-30.64373953100377</v>
+        <v>-30.49639832135049</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-31.57248232526</v>
+        <v>-31.4206747412547</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-27.27335704439176</v>
+        <v>-27.14648639253448</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-29.12969485562463</v>
+        <v>-28.99428298378209</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-29.60148768755537</v>
+        <v>-29.46419780749552</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>143</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.542389369161022</v>
+        <v>-3.52961079721733</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-7.254455016463055</v>
+        <v>-7.22078584279771</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.45147317130454</v>
+        <v>-10.40248535269863</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-13.82562771938275</v>
+        <v>-13.75871770885517</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-15.77099845095246</v>
+        <v>-15.69368455989499</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-16.88146087819045</v>
+        <v>-16.79542205282861</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-16.27105382514189</v>
+        <v>-16.19034162455046</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-15.34405142136721</v>
+        <v>-15.26666914249083</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-16.81572790427975</v>
+        <v>-16.72839621330348</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-20.48361518133094</v>
+        <v>-20.3762902523892</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-19.99490612183715</v>
+        <v>-19.89072387565321</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-23.47925070036312</v>
+        <v>-23.35827455730661</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-26.01922841957186</v>
+        <v>-25.88469419387798</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-26.48121456696436</v>
+        <v>-26.34462234749469</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>143</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.143787970559465</v>
+        <v>-2.13788778242543</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.057014116549496</v>
+        <v>-3.044622096307315</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6530051083167479</v>
+        <v>-0.6576960627679966</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5221083259058901</v>
+        <v>-0.528024778022008</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.462300709431908</v>
+        <v>-2.456436296498069</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.86674931308761</v>
+        <v>-2.8553241933569</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.652838547773918</v>
+        <v>-3.638865508752865</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.825320170583566</v>
+        <v>-4.802205019785674</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.081880833094921</v>
+        <v>-2.073414269157645</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.531797425271499</v>
+        <v>-1.526593093465991</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.737494178050795</v>
+        <v>-1.731583822425698</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9984024210111571</v>
+        <v>-0.9994205254534236</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.124053381571592</v>
+        <v>-2.118383022802753</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.390873007686395</v>
+        <v>-5.365601368473392</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>142</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.027688440353323</v>
+        <v>1.013513684465273</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.811218881053705</v>
+        <v>-4.785458136086916</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.207904163334327</v>
+        <v>-5.183216048904342</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.373930367806167</v>
+        <v>-4.355284638353197</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.503778175483497</v>
+        <v>-3.490192663694614</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.620086876929633</v>
+        <v>-4.595438636664205</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.23781373962693</v>
+        <v>-8.191563038871955</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-7.29823423395618</v>
+        <v>-7.25545629087339</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-10.19199969649679</v>
+        <v>-10.12878972344969</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-10.34338129636589</v>
+        <v>-10.27927654583515</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-11.26152927600445</v>
+        <v>-11.19191490635586</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-15.47881772472304</v>
+        <v>-15.38442707831138</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-15.90916495597842</v>
+        <v>-15.81170652476463</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-14.95731312396295</v>
+        <v>-14.86525664277688</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-7.717318917224986</v>
+        <v>-8.409451241299081</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-12.66113937114937</v>
+        <v>-13.95416135247928</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-11.16700234830139</v>
+        <v>-12.23815585310152</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-9.898920543759765</v>
+        <v>-10.81796726187655</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-13.00920114931689</v>
+        <v>-14.26757387293797</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-13.78990115237503</v>
+        <v>-15.20531164015444</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-16.45781124380511</v>
+        <v>-18.14823643015561</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-14.23940135740551</v>
+        <v>-15.73181613753574</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-13.86228715645163</v>
+        <v>-15.35991690897056</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-10.51168317608101</v>
+        <v>-11.64868447820862</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-8.791347772799838</v>
+        <v>-9.741043550950785</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-9.101477634942682</v>
+        <v>-10.06385469324278</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-8.313077737931181</v>
+        <v>-9.198061811392932</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-11.38942257354233</v>
+        <v>-12.61289952486243</v>
       </c>
     </row>
     <row r="22">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.01924</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4094</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.05099800801013998</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.05235</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3951~3964</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3951</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.2563094093561205</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.08546</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3809~3822</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3809</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.09682855577118943</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.1186</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3666~3679</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3666</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.1966185322241074</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.1517</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3524~3537</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3524</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.5567688262885682</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.1848</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3381~3394</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3381</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.8729315435452776</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.2179</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3239~3252</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3239</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.017423560062369</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.251</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3097~3110</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3097</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.110801664261423</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.2841</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2953~2966</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2953</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-1.111105211646247</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.3172</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2812~2825</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2812</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.236801152068381</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.3503</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2669~2682</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2669</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.225727656526153</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.3834</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2526~2539</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2526</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.607262660501434</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.4165</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2385~2398</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2385</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.325798620460183</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.4496</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2242~2255</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2242</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.185234329079158</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.4827</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2099~2112</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2099</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.12033225960392</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.5159</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1957~1970</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1957</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.275164208534854</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.549</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1836~1836</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1836</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.804985161168581</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.5821</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1737~1737</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1737</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.5072552459439947</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.6152</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1600~1600</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1600</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.05593832020997525</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.6483</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1462~1462</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1462</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.03734143355199393</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.6814</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1324~1324</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1324</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.3766523142311158</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.7145</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1187~1187</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1187</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.2445566250301212</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.7476</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1048~1048</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1048</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.08289755765261475</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.7807</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>911~911</t>
-        </is>
+      <c r="B29" t="n">
+        <v>911</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.1959140398339301</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.8138</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>774~774</t>
-        </is>
+      <c r="B30" t="n">
+        <v>774</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.2970558912694088</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.8469</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>635~635</t>
-        </is>
+      <c r="B31" t="n">
+        <v>635</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.15223097112861</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.88</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>498~498</t>
-        </is>
+      <c r="B32" t="n">
+        <v>498</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.731461278183602</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.9131</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>360~360</t>
-        </is>
+      <c r="B33" t="n">
+        <v>360</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>4.173228346456689</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.9462</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>222~222</t>
-        </is>
+      <c r="B34" t="n">
+        <v>222</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>5.61466978789813</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.9794</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>3.458942632170981</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.01924</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.05235</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>227~227</t>
-        </is>
+      <c r="B7" t="n">
+        <v>227</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-4.475817174835527</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.08546</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>369~369</t>
-        </is>
+      <c r="B8" t="n">
+        <v>369</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-1.00292341506092</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.1186</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>512~512</t>
-        </is>
+      <c r="B9" t="n">
+        <v>512</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1.412811679790025</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.1517</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>654~654</t>
-        </is>
+      <c r="B10" t="n">
+        <v>654</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3.011148835753325</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.1848</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>797~797</t>
-        </is>
+      <c r="B11" t="n">
+        <v>797</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.717352144030926</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.2179</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>939~939</t>
-        </is>
+      <c r="B12" t="n">
+        <v>939</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>3.523601083410895</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.251</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1081~1081</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1081</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>3.195738368041646</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.2841</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1225~1225</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1225</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.690235149177774</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.3172</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1366~1366</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1366</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.557806189306866</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.3503</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1509~1509</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1509</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2.178529870644894</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.3834</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1652~1652</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1652</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>2.470242067199223</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.4165</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1793~1793</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1793</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.773153983192145</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.4496</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1936~1936</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1936</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.380528621938794</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.4827</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2079~2079</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2079</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.138115311343654</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.5159</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2221~2221</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2221</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.131055151199298</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.549</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2342~2355</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2342</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.6275807880702757</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.5821</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2441~2454</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2441</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.3590474173613316</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.6152</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2578~2591</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2578</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.03454315412425046</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.6483</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2716~2729</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2716</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.02000482808831805</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.6814</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2854~2867</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2854</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.1739405873882163</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.7145</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2991~3004</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2991</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.09663405922461976</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.7476</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3130~3143</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3130</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.02764131098312106</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.7807</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3267~3280</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3267</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.05441392996607419</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.8138</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3404~3417</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3404</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.06728746264047203</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.8469</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3543~3556</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3543</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.3843269591301137</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.88</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3680~3693</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3680</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.5031864924276874</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.9131</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3818~3831</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3818</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.3921592807946794</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.9462</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3956~3969</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3956</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.3140480455816075</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.9794</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4094</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.07074535697646667</v>

--- a/workspaces/btc_daily_14days/cycle/cycle_phase.xlsx
+++ b/workspaces/btc_daily_14days/cycle/cycle_phase.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Cycle Phase is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Cycle Phase is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>143</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.621626794213384</v>
+        <v>-5.632926298359571</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.532985086416502</v>
+        <v>-6.520120032838761</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.41481991172969</v>
+        <v>-10.40185699892339</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.86770145192116</v>
+        <v>-15.85476598766358</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.31582471421817</v>
+        <v>-14.30275262803059</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-18.21010480397251</v>
+        <v>-18.19709810438142</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-16.90294214693365</v>
+        <v>-16.88990713867506</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-16.67553833671896</v>
+        <v>-16.66238417737939</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.74051033666773</v>
+        <v>-16.7273341147834</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-15.49831773085697</v>
+        <v>-15.48493050081679</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-12.91174609239396</v>
+        <v>-12.89830179835705</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-15.67651649984892</v>
+        <v>-15.66307322488116</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-13.30420994935406</v>
+        <v>-13.29065828088127</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.764202767074636</v>
+        <v>-6.774632402772788</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>142</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.534214841081649</v>
+        <v>4.522926510860628</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.332505561573335</v>
+        <v>4.345375850778126</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.642859172830676</v>
+        <v>4.655829597841127</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.988806383101576</v>
+        <v>9.001754880637449</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.07419154541006</v>
+        <v>14.0872776648524</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.86091742502042</v>
+        <v>10.87393669221075</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12.88796227850231</v>
+        <v>12.90100870580484</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.72150418304309</v>
+        <v>11.73466756021082</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.25707656109713</v>
+        <v>10.27025996909424</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.92766381664815</v>
+        <v>12.94105722434506</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.911567007945322</v>
+        <v>9.925014848201727</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.948374348818959</v>
+        <v>9.961820321261364</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.826550244173937</v>
+        <v>8.840103042665206</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.261503920603573</v>
+        <v>6.251074284905101</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>143</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.619744811650541</v>
+        <v>7.608463197217596</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.409166815417422</v>
+        <v>7.422037059162307</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.20156797561751</v>
+        <v>11.2145411646372</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.33469291269761</v>
+        <v>11.34764123719373</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.89269980709213</v>
+        <v>12.90578389711641</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.49559332389725</v>
+        <v>12.50861218270379</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>15.20623576096668</v>
+        <v>15.2192823276136</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.74386790274227</v>
+        <v>14.75703162638505</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>18.87727530483348</v>
+        <v>18.89046098633644</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>20.12850574954851</v>
+        <v>20.1419006580885</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>20.62813033013646</v>
+        <v>20.64157997864027</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.36696706557517</v>
+        <v>21.38041434673001</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23.04982655627104</v>
+        <v>23.06338020536792</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>26.10293010005775</v>
+        <v>26.09250046435977</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>142</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.741195807798185</v>
+        <v>8.729920085380371</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.242779264344257</v>
+        <v>9.255648640528761</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.06446704059424</v>
+        <v>13.07743988895283</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>16.00728126084461</v>
+        <v>16.02023153669099</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13.36663972220686</v>
+        <v>13.37972271936766</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>15.77565850122242</v>
+        <v>15.7886781390328</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>14.9925956632352</v>
+        <v>15.00564117355282</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>16.6396411793725</v>
+        <v>16.6528049642723</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>18.6932962695203</v>
+        <v>18.70648139734276</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>21.3663645795298</v>
+        <v>21.37975955642659</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>26.09342896278456</v>
+        <v>26.10687969171846</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>28.2468058647827</v>
+        <v>28.26025410955376</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>31.35485938982865</v>
+        <v>31.36841365527337</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>30.20516589243439</v>
+        <v>30.19473625673624</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>143</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.918379055144527</v>
+        <v>6.907106867699852</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.314261517149006</v>
+        <v>5.327124196805649</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.922402487619195</v>
+        <v>4.935365674769187</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.540048793897746</v>
+        <v>8.552991267039992</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.400039032997114</v>
+        <v>9.413117453575843</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.607156184257448</v>
+        <v>7.620169067104385</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.431381081251509</v>
+        <v>5.444419761480013</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.362924658299733</v>
+        <v>6.376082328439118</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.209350727830532</v>
+        <v>4.222529054305788</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.662873936504965</v>
+        <v>2.676262140716524</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.555434940063705</v>
+        <v>4.568880031687236</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.98932503429905</v>
+        <v>6.00276945173318</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.27041087691984</v>
+        <v>6.283963024385798</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>9.319713316841131</v>
+        <v>9.309283681143135</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>142</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.422911002221284</v>
+        <v>2.411639344817274</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.3424533367914</v>
+        <v>11.35531932962616</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.549029420737156</v>
+        <v>9.561994083295325</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.08567455457483</v>
+        <v>11.09861697181164</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.444883948552437</v>
+        <v>8.457959458407949</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.15008582564309</v>
+        <v>10.16309855044892</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.663661091314921</v>
+        <v>8.676699858679186</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.903119631365847</v>
+        <v>8.916277054700238</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.626625877345511</v>
+        <v>4.639802817929649</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.778975090242142</v>
+        <v>3.792362360992726</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.168720504845062</v>
+        <v>2.182163986917338</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.204215484580452</v>
+        <v>2.217658609053565</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.785227640590179</v>
+        <v>1.798779082515487</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.07652424841051442</v>
+        <v>-0.08695388410882998</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>142</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.019139740673246</v>
+        <v>1.007872149082516</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.517196765472313</v>
+        <v>1.530047857242423</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.44057791195555</v>
+        <v>7.453537336268589</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.062644825126092</v>
+        <v>4.075577701264066</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.633644159928132</v>
+        <v>5.64671462142018</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.825822850393017</v>
+        <v>3.838828384633338</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.74325356682801</v>
+        <v>3.756286866807294</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.2784839365954</v>
+        <v>3.291636248610232</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.735072122053289</v>
+        <v>6.748248430692477</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.591644840511968</v>
+        <v>6.605031840565545</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.389655462401372</v>
+        <v>6.403099103986861</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.315301763866174</v>
+        <v>4.328744561607159</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.193113446216167</v>
+        <v>3.206664648464162</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.07652424841051442</v>
+        <v>-0.08695388410851024</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>144</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.10457683490457</v>
+        <v>-1.115841025164819</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.094923179260249</v>
+        <v>-4.082085059898731</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.489850366582957</v>
+        <v>-4.476909507847751</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.285015574991256</v>
+        <v>-2.272093813105059</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.715944740884723</v>
+        <v>2.72900901606652</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4480189070071745</v>
+        <v>-0.435020422513233</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.703396669657458</v>
+        <v>5.716428751941095</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.774341219447287</v>
+        <v>1.787490043460494</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.408174473448767</v>
+        <v>2.421346571368197</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.560250332676894</v>
+        <v>1.573633628391946</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.438045266962206</v>
+        <v>3.451486836032309</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.474320128663976</v>
+        <v>3.487761948447002</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.667637229040963</v>
+        <v>1.681187845572296</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.918780915908734</v>
+        <v>1.908351280210738</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>141</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.395681912233592</v>
+        <v>1.384428719468616</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4964351288991367</v>
+        <v>0.5092725895202648</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1031284485909865</v>
+        <v>0.1160686212593092</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.886409500767016</v>
+        <v>5.899335717519705</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4021007340116824</v>
+        <v>0.4151582208281184</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.822405351978112</v>
+        <v>2.83540279436707</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.739100450825383</v>
+        <v>2.752127107235758</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.690288745688157</v>
+        <v>3.703436038467046</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.587356872241024</v>
+        <v>8.600530433344176</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>7.741849805336862</v>
+        <v>7.755234193266638</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.249112150270605</v>
+        <v>8.262554158426042</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9.70471987796239</v>
+        <v>9.718162351808836</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.997864019753159</v>
+        <v>10.01141519031641</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.24168461354375</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>143</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.443480589846097</v>
+        <v>-1.454730064206409</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.657161334819648</v>
+        <v>-1.644334809049447</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.127476543679556</v>
+        <v>2.140413009964412</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5300262479513549</v>
+        <v>-0.5171135122554418</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.720903765446138</v>
+        <v>1.7339576175074</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5.505945369959576</v>
+        <v>5.518941543753648</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.818737799398754</v>
+        <v>6.831764743398871</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.449382324307841</v>
+        <v>8.462530531264711</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>6.996300708297468</v>
+        <v>7.009471234132391</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.055926372438066</v>
+        <v>4.069307060389526</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.456651723596266</v>
+        <v>2.470090129424072</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.68567174401857</v>
+        <v>6.69911267476612</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.667252997935769</v>
+        <v>7.680803503566779</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.921111918239731</v>
+        <v>7.910682282541579</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>143</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5.513834721386786</v>
+        <v>5.502608666810616</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.998809706117676</v>
+        <v>6.011641161971816</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6.999553453218638</v>
+        <v>7.012491029731137</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.524296434923428</v>
+        <v>8.537216105617894</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.203368555839205</v>
+        <v>5.216421520811608</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.714942864216844</v>
+        <v>2.727931320879684</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.026512030905359</v>
+        <v>4.039532574047449</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.167827459542671</v>
+        <v>2.180967165552737</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7130007113328674</v>
+        <v>0.7261639404662219</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.960178486725148</v>
+        <v>1.973555561888581</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3605365596317824</v>
+        <v>0.3739721240095761</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.3026368287120462</v>
+        <v>-0.2891990402341875</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.721502897346582</v>
+        <v>-0.707954146914723</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.267699270571455</v>
+        <v>-3.278128906269608</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>141</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.368196954816035</v>
+        <v>-6.379435663078539</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-12.20975476084194</v>
+        <v>-12.19696899994176</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-11.19721762354018</v>
+        <v>-11.18432136230004</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-16.01713197741618</v>
+        <v>-16.00426015820277</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-17.97298791776321</v>
+        <v>-17.95997691413991</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-20.50929741393178</v>
+        <v>-20.49634710460685</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-22.01650754385904</v>
+        <v>-22.00352340174464</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-26.73478993618928</v>
+        <v>-26.72168491903898</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-31.05188383233067</v>
+        <v>-31.03875229747266</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-30.49639832135049</v>
+        <v>-30.48304695047501</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-31.4206747412547</v>
+        <v>-31.40725827333451</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-27.14648639253448</v>
+        <v>-27.13305962175604</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-28.99428298378209</v>
+        <v>-28.98074000353405</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-29.46419780749552</v>
+        <v>-29.47462744319368</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>143</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.52961079721733</v>
+        <v>-3.540831838033348</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-7.22078584279771</v>
+        <v>-7.208006744211914</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.40248535269863</v>
+        <v>-10.38960359309633</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-13.75871770885517</v>
+        <v>-13.74585801828528</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-15.69368455989499</v>
+        <v>-15.68068520824112</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-16.79542205282861</v>
+        <v>-16.78248084412137</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-16.19034162455046</v>
+        <v>-16.17736284278902</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-15.26666914249083</v>
+        <v>-15.25356339480692</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-16.72839621330348</v>
+        <v>-16.71526223640753</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-20.3762902523892</v>
+        <v>-20.36294019625443</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-19.89072387565321</v>
+        <v>-19.87730767668324</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-23.35827455730661</v>
+        <v>-23.34485061069162</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-25.88469419387798</v>
+        <v>-25.87115283718791</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-26.34462234749469</v>
+        <v>-26.35505198319284</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>143</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.13788778242543</v>
+        <v>-2.149090458382403</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.044622096307315</v>
+        <v>-3.031851398713442</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6576960627679966</v>
+        <v>-0.6448097725356305</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.528024778022008</v>
+        <v>-0.5151547286214893</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.456436296498069</v>
+        <v>-2.443428604614482</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.8553241933569</v>
+        <v>-2.842374999129547</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.638865508752865</v>
+        <v>-3.625881544587415</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.802205019785674</v>
+        <v>-4.789097599952349</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.073414269157645</v>
+        <v>-2.060274681433867</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.526593093465991</v>
+        <v>-1.513235589010051</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.731583822425698</v>
+        <v>-1.718162428480198</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9994205254534236</v>
+        <v>-0.9859915062869078</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.118383022802753</v>
+        <v>-2.104838947710611</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.365601368473392</v>
+        <v>-5.376031004171544</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>142</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.013513684465273</v>
+        <v>1.002339990680589</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.785458136086916</v>
+        <v>-4.772713827973007</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.183216048904342</v>
+        <v>-5.170359874948986</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.355284638353197</v>
+        <v>-4.342439988083903</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.490192663694614</v>
+        <v>-3.477202629378674</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.595438636664205</v>
+        <v>-4.582507164915704</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.191563038871955</v>
+        <v>-8.178599854843121</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-7.25545629087339</v>
+        <v>-7.24236417049633</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-10.12878972344969</v>
+        <v>-10.11566944966295</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-10.27927654583515</v>
+        <v>-10.26593519622976</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-11.19191490635586</v>
+        <v>-11.17850622651531</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-15.38442707831138</v>
+        <v>-15.37100893164047</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-15.81170652476463</v>
+        <v>-15.79816779547653</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-14.86525664277688</v>
+        <v>-14.8756862784747</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.409451241299081</v>
+        <v>-7.9650932054397</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-13.95416135247928</v>
+        <v>-14.26768671209777</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-12.23815585310152</v>
+        <v>-12.56911547190311</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-10.81796726187655</v>
+        <v>-11.15976045326285</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-14.26757387293797</v>
+        <v>-14.58557106978532</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-15.20531164015444</v>
+        <v>-15.51346202541018</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-18.14823643015561</v>
+        <v>-18.4331606613739</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-15.73181613753574</v>
+        <v>-16.04046505748298</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-15.35991690897056</v>
+        <v>-15.67231447515793</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.64868447820862</v>
+        <v>-11.99848017039549</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-9.741043550950785</v>
+        <v>-10.10833370504385</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-10.06385469324278</v>
+        <v>-10.42845912169869</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-9.198061811392932</v>
+        <v>-9.573336302667805</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-12.61289952486243</v>
+        <v>-12.16268697115572</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>99</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.028791855563625</v>
+        <v>-6.04012452772006</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.620163448325748</v>
+        <v>-5.607253638749697</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.196029058493366</v>
+        <v>2.20900820089183</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.372695186881955</v>
+        <v>-1.359584382507016</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.9449487710356053</v>
+        <v>0.9579916673299707</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.170087976539577</v>
+        <v>-2.157021722239101</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.627170365220309</v>
+        <v>-1.613989355925071</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.688170251402376</v>
+        <v>-1.674971512447613</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.568598466733455</v>
+        <v>-5.555193339080624</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.793553811252707</v>
+        <v>-7.780096517542489</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-10.78947368421053</v>
+        <v>-10.77602139549042</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-11.20972829515566</v>
+        <v>-11.19617224880406</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.919602922475107</v>
+        <v>-6.930032558173259</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>137</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-5.778109853056606</v>
+        <v>-5.78944252521304</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.389683466020948</v>
+        <v>-7.376773656444897</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-10.70426020181453</v>
+        <v>-10.69125307039693</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-9.844080061907931</v>
+        <v>-9.831100919509467</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-14.03213631347636</v>
+        <v>-14.01902550910143</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-10.81498634656362</v>
+        <v>-10.80194345026926</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-13.8194280930329</v>
+        <v>-13.80636183873243</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-14.28661149181448</v>
+        <v>-14.27343048251925</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-15.07753838529606</v>
+        <v>-15.0643396463413</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-13.73788254842601</v>
+        <v>-13.72447742077318</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-14.67256288004302</v>
+        <v>-14.65910558633281</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-13.17832570809913</v>
+        <v>-13.16487341937902</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-17.97814236283957</v>
+        <v>-17.96458631648797</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-17.72842103056328</v>
+        <v>-17.73885066626143</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>138</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.044162957891139</v>
+        <v>-1.055495630047574</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.554287295493154</v>
+        <v>-5.541377485917103</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.050605277451986</v>
+        <v>-3.037598146034384</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.818902869482166</v>
+        <v>-5.805923727083702</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.059882146838675</v>
+        <v>-6.046839250544309</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.072152095995094</v>
+        <v>-1.059085841694618</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-4.437886219414111</v>
+        <v>-4.424705210118873</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.49888610559649</v>
+        <v>-4.485687366641727</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.349011290624503</v>
+        <v>-5.335606162971672</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.003039977260762</v>
+        <v>-6.989582683550545</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-10.59184522571243</v>
+        <v>-10.57839293699232</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-11.73673751781683</v>
+        <v>-11.72318147146523</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-12.21165386669996</v>
+        <v>-12.22208350239811</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>138</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.21807600136939</v>
+        <v>-3.229408673525825</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.692089516101134</v>
+        <v>1.704999325677186</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.920352144844486</v>
+        <v>-2.907373002446022</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.009497997597812</v>
+        <v>-1.996387193222873</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.335244465679246</v>
+        <v>-5.32220156938488</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.09006013245774369</v>
+        <v>-0.07687912316250589</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.600335380958803</v>
+        <v>-1.58713664200404</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.175098247146082</v>
+        <v>-3.16169311949325</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.930576209144981</v>
+        <v>-1.917118915434763</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.620830732958879</v>
+        <v>-2.607378444238769</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.591809981585023</v>
+        <v>-1.57825393523342</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1071867130101793</v>
+        <v>0.09675707731202721</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>137</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.521160219936085</v>
+        <v>1.509827547779651</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>7.208856679964533</v>
+        <v>7.221766489540585</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.9745719149737013</v>
+        <v>0.9875790463913035</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.084955974316529</v>
+        <v>-1.071976831918064</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.75618485440684</v>
+        <v>2.769295658781779</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.97333482131959</v>
+        <v>5.986377717613955</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.348455118645852</v>
+        <v>7.361521372946328</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>9.071052741762237</v>
+        <v>9.084233751057475</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>11.19983387747767</v>
+        <v>11.21303261643243</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>12.53948971434747</v>
+        <v>12.5528948420003</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>13.79459040462851</v>
+        <v>13.80804769833873</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>14.55890056927321</v>
+        <v>14.57235285799332</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>16.3284269802262</v>
+        <v>16.34198302657781</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>15.11829429790387</v>
+        <v>15.10786466220572</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>139</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.46339621216412</v>
+        <v>1.452063540007686</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.607218282653193</v>
+        <v>5.620128092229244</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.054076194761471</v>
+        <v>3.067083326179073</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.781451629527325</v>
+        <v>6.794430771925789</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.523605954023502</v>
+        <v>5.536716758398441</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.101623431307502</v>
+        <v>5.114666327601867</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.455738634898537</v>
+        <v>6.468804889199014</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.427404156980344</v>
+        <v>7.440585166275582</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.24410211252475</v>
+        <v>10.25730085147951</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>16.58822153181329</v>
+        <v>16.60162665946612</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>14.9446192866324</v>
+        <v>14.95807658034262</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>16.41785136484114</v>
+        <v>16.43130365356125</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>15.99759675389631</v>
+        <v>16.01115280024791</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>16.9667425466041</v>
+        <v>16.95631291090594</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>137</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.668620801961886</v>
+        <v>-0.6799534741183209</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.280194414926186</v>
+        <v>-2.267284605350135</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7.784552172617374</v>
+        <v>-7.771545041199772</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.464518018112351</v>
+        <v>-5.451538875713887</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.813158211286584</v>
+        <v>-3.800047406911645</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.055862258972383</v>
+        <v>-2.042819362678017</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.600449990843202</v>
+        <v>-3.587383736542726</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.717268426121223</v>
+        <v>-7.704087416825985</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-7.048341305004165</v>
+        <v>-7.035142566049402</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.708685468134291</v>
+        <v>-5.69528034048146</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.643365799751052</v>
+        <v>-6.629908506040834</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-8.798763664303436</v>
+        <v>-8.785311375583326</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-7.759164260649875</v>
+        <v>-7.745608214298272</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.589734899176257</v>
+        <v>-4.600164534874409</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>137</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.981014234534548</v>
+        <v>2.969681562378113</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.289148650767416</v>
+        <v>4.302058460343467</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.084060966068506</v>
+        <v>6.097068097486108</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.834752054880518</v>
+        <v>1.847731197278982</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.216038869005388</v>
+        <v>4.229149673380327</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.243407814020273</v>
+        <v>5.256450710314638</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.698820082149489</v>
+        <v>3.711886336449965</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.041855661470272</v>
+        <v>1.05503667076551</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4789982393106555</v>
+        <v>-0.4657995003558923</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.059050431637807</v>
+        <v>-2.045645303984976</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.263803755955436</v>
+        <v>-2.250346462245219</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-4.419201620507806</v>
+        <v>-4.405749331787696</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.839456231452708</v>
+        <v>-4.825900185101105</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.58973489917647</v>
+        <v>-4.600164534874622</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>139</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-11.48624407560566</v>
+        <v>-11.4975767477621</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-8.781270925979989</v>
+        <v>-8.768361116403938</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-8.456715172144918</v>
+        <v>-8.443708040727316</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-9.765310960400733</v>
+        <v>-9.752331818002268</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-8.145458794177941</v>
+        <v>-8.132347989803002</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.128592396030577</v>
+        <v>-7.115549499736211</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-9.371599494597824</v>
+        <v>-9.358533240297348</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-7.680509512084406</v>
+        <v>-7.667328502789168</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.302660477403393</v>
+        <v>-6.28946173844863</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-7.152785662431285</v>
+        <v>-7.139380534778454</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-8.076963447180553</v>
+        <v>-8.063506153470335</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-8.762004750266783</v>
+        <v>-8.748552461546673</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.304561519485063</v>
+        <v>-6.29100547313346</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-10.37138694979878</v>
+        <v>-10.38181658549694</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>137</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.588328831158876</v>
+        <v>-3.599661503315311</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-7.389683466020948</v>
+        <v>-7.376773656444897</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.324698158019039</v>
+        <v>-6.311691026601437</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.814882981615874</v>
+        <v>-1.80190383921741</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.273012225885125</v>
+        <v>-5.259901421510186</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.785789266271649</v>
+        <v>-2.772746369977284</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.600449990843245</v>
+        <v>-3.587383736542769</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.797560396923934</v>
+        <v>-4.784379387628697</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-7.048341305004129</v>
+        <v>-7.035142566049366</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-7.898466490032014</v>
+        <v>-7.885061362379183</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-7.373292807050284</v>
+        <v>-7.359835513340066</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-5.879055635106312</v>
+        <v>-5.865603346386202</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.109529224153441</v>
+        <v>-4.095973177801838</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.39995387727857</v>
+        <v>-2.410383512976722</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>138</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.57902544790597</v>
+        <v>2.567692775749535</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.764553284217079</v>
+        <v>6.777463093793131</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.81895993993939</v>
+        <v>7.831967071356992</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.499937710227989</v>
+        <v>6.512916852626454</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.236878813996391</v>
+        <v>5.24998961837133</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.98359611403091</v>
+        <v>6.996639010325275</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.34813775907746</v>
+        <v>8.361204013377936</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.330229722614753</v>
+        <v>9.343410731909991</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>16.51560664802674</v>
+        <v>16.5288053869815</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.4915684195205</v>
+        <v>13.50497354717334</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.28681509520288</v>
+        <v>13.3002723889131</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.04583593370772</v>
+        <v>14.05928822242783</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.17630596044403</v>
+        <v>12.18986200679564</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.70138961156091</v>
+        <v>11.69095997586276</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>138</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.854387766746541</v>
+        <v>1.843055094590106</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.416727197260549</v>
+        <v>2.4296370068366</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.74649617182336</v>
+        <v>2.759503303240962</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.471076782525643</v>
+        <v>-1.458097640127178</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.009497997597833</v>
+        <v>-1.996387193222894</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.4618569835961139</v>
+        <v>0.4748998798904793</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.000311672120937</v>
+        <v>4.013377926421413</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.330229722614796</v>
+        <v>9.343410731910033</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.544592155273065</v>
+        <v>8.557790894227828</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.419104651404567</v>
+        <v>8.432509779057398</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.48971364592758</v>
+        <v>7.503170939637798</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.14728520907012</v>
+        <v>11.16073749779023</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.90094364160345</v>
+        <v>12.91449968795506</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.70138961156091</v>
+        <v>11.69095997586276</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.9628</t>
+          <t>X ≈ 0.9627</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>138</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.926851534862486</v>
+        <v>6.915518862706051</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>8.213828646535909</v>
+        <v>8.22673845611196</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.543597621098748</v>
+        <v>8.55660475251635</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.12312611602508</v>
+        <v>10.13610525842355</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>13.20789330675004</v>
+        <v>13.22100411112498</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.05605988214681</v>
+        <v>12.06910277844118</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.14523920835281</v>
+        <v>14.15830546265329</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>14.40269349073073</v>
+        <v>14.41587450002597</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.8924182422296</v>
+        <v>12.90561698118437</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.76693073836108</v>
+        <v>12.78033586601391</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.18536581984058</v>
+        <v>16.1988231135508</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.21974897718604</v>
+        <v>16.23320126590615</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>16.52413204740056</v>
+        <v>16.53768809375217</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>16.77385337967685</v>
+        <v>16.7634237439787</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Cycle Phase is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Cycle Phase is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.05099800801013998</v>
+        <v>0.05121732311557281</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0865024348790584</v>
+        <v>-0.0867454155387648</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04335931150811234</v>
+        <v>0.04308265336134554</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08943682032206368</v>
+        <v>0.08914944278690484</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.07610921098410017</v>
+        <v>0.07582231605757528</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.003098252096620513</v>
+        <v>-0.00336452190813219</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.120558059534396</v>
+        <v>0.1202611011187997</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.08137853845078524</v>
+        <v>0.08108871076990454</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2290256155373243</v>
+        <v>0.2286993424427592</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1977029071815082</v>
+        <v>0.1973799665545215</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2751734910599168</v>
+        <v>0.2748304978528182</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2501214862440122</v>
+        <v>0.2497846266543817</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2099631245359816</v>
+        <v>0.2096338591507134</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2048906700204398</v>
+        <v>0.2050545769138736</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3951</v>
+        <v>3952</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2563094093561205</v>
+        <v>0.2568935725768426</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1468174889806946</v>
+        <v>0.1460411660082741</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4218760487703221</v>
+        <v>0.4210245486742821</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.6669794102817619</v>
+        <v>0.6660674353361031</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5970017828150134</v>
+        <v>0.5960996989028828</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.6558746501859076</v>
+        <v>0.6549613642997869</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.7366958802190098</v>
+        <v>0.7357606097955554</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.6878678103184797</v>
+        <v>0.6869380586963629</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.8432102880671408</v>
+        <v>0.8422400267502823</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.7657947703147627</v>
+        <v>0.7648319900449252</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7524525344499153</v>
+        <v>0.751489890149891</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8265601680995616</v>
+        <v>0.8255788252296767</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.699086574185749</v>
+        <v>0.6981312721123913</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4571256387636993</v>
+        <v>0.4576090399946509</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3809</v>
+        <v>3810</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.09682855577118943</v>
+        <v>0.09789706936521725</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.009225489834790324</v>
+        <v>-0.01046947053695391</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2645172659883457</v>
+        <v>0.2631919195452355</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3567406520406493</v>
+        <v>0.3553935200518978</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.09457045010604759</v>
+        <v>0.09327889282286606</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.2754293695278491</v>
+        <v>0.2740966670390677</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2836951376208887</v>
+        <v>0.2823576623852375</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2765324559139373</v>
+        <v>0.2751854106084153</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.4922601670983155</v>
+        <v>0.4908545065894216</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3123987596612139</v>
+        <v>0.3110199209450286</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4109995926708763</v>
+        <v>0.4095894848891604</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4864977859356969</v>
+        <v>0.4850679873198445</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3960937043673525</v>
+        <v>0.3946772061232906</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.240737684964472</v>
+        <v>0.2416846135439101</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1966185322241074</v>
+        <v>-0.1949883836707542</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2985954024510065</v>
+        <v>-0.3003108759765496</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1621052794227182</v>
+        <v>-0.1638718770318519</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.07147734394242633</v>
+        <v>-0.07326517194462667</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.404647361691282</v>
+        <v>-0.4063633803197533</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2012436925220129</v>
+        <v>-0.2030060650962113</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2983897803110338</v>
+        <v>-0.30012944618516</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2877962317283007</v>
+        <v>-0.2895552517466555</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2248858134516354</v>
+        <v>-0.2266649170821893</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4605699527102658</v>
+        <v>-0.4623141247085059</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3776118899962171</v>
+        <v>-0.3793864192849341</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3279886044048439</v>
+        <v>-0.3297764439306761</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4875625416288969</v>
+        <v>-0.4893218472969423</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.7680712390285365</v>
+        <v>-0.7664055600766702</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3524</v>
+        <v>3525</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5567688262885682</v>
+        <v>-0.5545166113601852</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6830662318167668</v>
+        <v>-0.6852601671378977</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6950715874370204</v>
+        <v>-0.6972807481722256</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7193728382329354</v>
+        <v>-0.7215705712712221</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.959563016036789</v>
+        <v>-0.9617177707185078</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.845034870590041</v>
+        <v>-0.8472100812625385</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.9145418611803819</v>
+        <v>-0.9167023335618438</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9698893396670911</v>
+        <v>-0.9720560037111099</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9871962152058984</v>
+        <v>-0.9893618749966109</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.340088881080888</v>
+        <v>-1.342193404913097</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.444265636050382</v>
+        <v>-1.446350898082805</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.479413353163253</v>
+        <v>-1.481488313035591</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.770656728424292</v>
+        <v>-1.772668922861477</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.016141520716317</v>
+        <v>-2.013634535392249</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8729315435452776</v>
+        <v>-0.8700139967846638</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9367242821279547</v>
+        <v>-0.9394798489959442</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9326636586387522</v>
+        <v>-0.9354440948548444</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.111001733055382</v>
+        <v>-1.113723836462974</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.397724238459688</v>
+        <v>-1.400393535672407</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.202521803699526</v>
+        <v>-1.205233504744641</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.182943807577232</v>
+        <v>-1.185667578857817</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.280032019853202</v>
+        <v>-1.282754933781327</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.206985098037663</v>
+        <v>-1.209734554739441</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.509394909745431</v>
+        <v>-1.512104446611808</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.698024045510394</v>
+        <v>-1.700690940352793</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.795304979725543</v>
+        <v>-1.797942736560699</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.110755121670138</v>
+        <v>-2.113324856763413</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.495593529521614</v>
+        <v>-2.492397783459836</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.017423560062369</v>
+        <v>-1.013839544472162</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.475051920870321</v>
+        <v>-1.478325985836797</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.392188332078511</v>
+        <v>-1.395517002662665</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.645712456378469</v>
+        <v>-1.648956057072546</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.829230988245342</v>
+        <v>-1.832457154548763</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.700227973309488</v>
+        <v>-1.703475218274733</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.614625775975718</v>
+        <v>-1.617907139391846</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.726468430619832</v>
+        <v>-1.729749545622184</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.462734637557396</v>
+        <v>-1.466103167986049</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.741240707830713</v>
+        <v>-1.744584164722873</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.867544800728197</v>
+        <v>-1.870865446424503</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.970646722834971</v>
+        <v>-1.973935141214163</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.281557700318174</v>
+        <v>-2.284781263978722</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.601647199764834</v>
+        <v>-2.597821559295589</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.110801664261423</v>
+        <v>-1.106506768644131</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.612248986889256</v>
+        <v>-1.616217879225189</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.797177937068128</v>
+        <v>-1.801122463001015</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.907445337868189</v>
+        <v>-1.911345919462413</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.171409958552296</v>
+        <v>-2.175272645894019</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.953601953601954</v>
+        <v>-1.957512375025203</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.860288955400357</v>
+        <v>-1.864238820760555</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.955949617621634</v>
+        <v>-1.95990990158765</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.838610827374865</v>
+        <v>-1.842616378771183</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.123310371332373</v>
+        <v>-2.127297357993029</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.246144231585291</v>
+        <v>-2.250111077850725</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.258862636658534</v>
+        <v>-2.262824914552006</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.532575880107601</v>
+        <v>-2.536487306447057</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.717426166213755</v>
+        <v>-2.712909748410034</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.111105211646247</v>
+        <v>-1.106051747337766</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.491183939919594</v>
+        <v>-1.496013114832166</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.665872542604824</v>
+        <v>-1.67068463820145</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.889033514588228</v>
+        <v>-1.893760375561079</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.409736770851289</v>
+        <v>-2.414343925285458</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.027020158380012</v>
+        <v>-2.031729992209264</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.229124285575885</v>
+        <v>-2.233777118143443</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.137853403784149</v>
+        <v>-2.142586134521615</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.045700933476667</v>
+        <v>-2.050473746685903</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.302935410742244</v>
+        <v>-2.307708347173609</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.523327871202909</v>
+        <v>-2.528049500193021</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.53843538241081</v>
+        <v>-2.543151423784181</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.737394941305496</v>
+        <v>-2.742088261724916</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.943506023926467</v>
+        <v>-2.938184490495814</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.236801152068381</v>
+        <v>-1.230885642047937</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.590847627225223</v>
+        <v>-1.596526902359251</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.754574228151981</v>
+        <v>-1.760244613169085</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.278911702769271</v>
+        <v>-2.284384815349334</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.550728622979918</v>
+        <v>-2.556171085826527</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.270181252604942</v>
+        <v>-2.275692211515079</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.478242239997151</v>
+        <v>-2.483692687207949</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.430089549970347</v>
+        <v>-2.435614618841342</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.578866349766209</v>
+        <v>-2.584349178390212</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.806603517238379</v>
+        <v>-2.81210752890204</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.063482225053463</v>
+        <v>-3.068922275118474</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.152334703787979</v>
+        <v>-3.15774269373037</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.375969448243367</v>
+        <v>-3.381350254877361</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.605164081720481</v>
+        <v>-3.598817815653859</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.225727656526153</v>
+        <v>-1.218896970748816</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.587294663498746</v>
+        <v>-1.593966403985952</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.962567206935006</v>
+        <v>-1.969156238677733</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.372613696039771</v>
+        <v>-2.379036424466349</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.779594652033843</v>
+        <v>-2.785942023870255</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.686811491281134</v>
+        <v>-2.693157614887156</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.976356944243527</v>
+        <v>-2.982610444727349</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.012991190293235</v>
+        <v>-3.019298048229047</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.091885791243577</v>
+        <v>-3.098175515090865</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.174284961308715</v>
+        <v>-3.180662692298554</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.35924061945471</v>
+        <v>-3.365580991916076</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.679436585405185</v>
+        <v>-3.685656670395161</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.96764453621774</v>
+        <v>-3.973817665910133</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.222720270553118</v>
+        <v>-4.215244225407403</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.607262660501434</v>
+        <v>-1.599259181342795</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.016753461937043</v>
+        <v>-2.024358917611579</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.469923998068019</v>
+        <v>-2.477417243577811</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.989501324198024</v>
+        <v>-2.99677449799308</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.231520122629973</v>
+        <v>-3.23878649830219</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.99261152011573</v>
+        <v>-2.999930752130787</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.372798061997408</v>
+        <v>-3.379985376141988</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.306283774191307</v>
+        <v>-3.313575027085712</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.30728514590249</v>
+        <v>-3.314590450644751</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.464953319609933</v>
+        <v>-3.47233392710217</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.569821829513835</v>
+        <v>-3.577197966818083</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.870601417236998</v>
+        <v>-3.877858269569288</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.151412649582177</v>
+        <v>-4.15862909575435</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.276785196521992</v>
+        <v>-4.268274494753143</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.325798620460183</v>
+        <v>-1.316775994450616</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.414148353699886</v>
+        <v>-1.423211381312946</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.953970790021238</v>
+        <v>-1.962885189621467</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.219314354762481</v>
+        <v>-2.228100785466026</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.360011963672413</v>
+        <v>-2.36884188445763</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.957033863500186</v>
+        <v>-1.965984940857048</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.270591337912506</v>
+        <v>-2.279432626095897</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.921202277821621</v>
+        <v>-1.930279346127868</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.667038431107379</v>
+        <v>-1.676238891381239</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.866867891834069</v>
+        <v>-1.876143425720969</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.923293418379473</v>
+        <v>-1.932588367816059</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.494542808634492</v>
+        <v>-2.503598675831519</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.682714654981687</v>
+        <v>-2.691773421824365</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.78771803587324</v>
+        <v>-2.778712145327283</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.185234329079158</v>
+        <v>-1.174983758323854</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.043787443378314</v>
+        <v>-1.054408110294411</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.415104785354487</v>
+        <v>-1.425649018557301</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.483304238957288</v>
+        <v>-1.493798830810135</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.50955916204002</v>
+        <v>-1.520159942727339</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.01060678451983</v>
+        <v>-1.021375527496907</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.382757131405278</v>
+        <v>-1.39338535860275</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.069997210182144</v>
+        <v>-1.080868013554934</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.7063898303696234</v>
+        <v>-0.7174424855235699</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6862936734757312</v>
+        <v>-0.6975380141354606</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7772887103553217</v>
+        <v>-0.7885425090697353</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.163805235012674</v>
+        <v>-1.174887562730753</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.202838172349132</v>
+        <v>-1.213997560746797</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.285203621706486</v>
+        <v>-1.275628508762516</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.12033225960392</v>
+        <v>-1.108651730653207</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.907475220715682</v>
+        <v>-0.9197536387496967</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.466705284320589</v>
+        <v>-1.478820452929256</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.548385212236816</v>
+        <v>-1.560439833959173</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.445050619768693</v>
+        <v>-1.457289743370268</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8849304674813894</v>
+        <v>-0.897374134904787</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.229053702171974</v>
+        <v>-1.241362999271423</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.8157305514049682</v>
+        <v>-0.8283552369573854</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6132576270600936</v>
+        <v>-0.626002007421107</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6290460236145563</v>
+        <v>-0.641992893560662</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7122747984801094</v>
+        <v>-0.7252398193194054</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.175004383877358</v>
+        <v>-1.187750484669557</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.140464225891371</v>
+        <v>-1.153335504396402</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.007215590364098</v>
+        <v>-0.9964106245513236</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.275164208534854</v>
+        <v>-1.261747146602843</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6260886218486874</v>
+        <v>-0.6403254738519877</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.197035111315536</v>
+        <v>-1.211099003528439</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.344716475134859</v>
+        <v>-1.35868088509006</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.296655029458279</v>
+        <v>-1.310799636213375</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6156958430440014</v>
+        <v>-0.630117296160364</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7238537400813172</v>
+        <v>-0.7382538912575356</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3484637885002542</v>
+        <v>-0.363192178447413</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.07718977083838041</v>
+        <v>0.06221697970777029</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.0711750975685348</v>
+        <v>0.05596410693933507</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.04812831614347601</v>
+        <v>0.03286223881226391</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1439680923037159</v>
+        <v>-0.1591382786073083</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.07591828494093278</v>
+        <v>-0.09124858645290601</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.00167556509961031</v>
+        <v>0.01015584268929359</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1836</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.804985161168581</v>
+        <v>-0.8163178333250158</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2522865417713049</v>
+        <v>0.2651963513473561</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4693795504461988</v>
+        <v>-0.4563724190285967</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7203900343964378</v>
+        <v>-0.7074108919979736</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.441817785416319</v>
+        <v>-0.4287069810413797</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.345820230730709</v>
+        <v>0.3588631270250744</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4244852062688906</v>
+        <v>0.4375514605693667</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6653628096660356</v>
+        <v>0.6785438189612734</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.094559001915108</v>
+        <v>1.107757740869872</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.843562357192198</v>
+        <v>0.856967484845029</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6932752638114437</v>
+        <v>0.7067325575216614</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5097934974095892</v>
+        <v>0.5232457861296993</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.525268733959237</v>
+        <v>0.5388247803108399</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8294562971723494</v>
+        <v>0.8190266614741972</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1737</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5072552459439947</v>
+        <v>-0.5185879181004296</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5869857640048082</v>
+        <v>0.5998955735808593</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5562997531847458</v>
+        <v>-0.5432926217671437</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.8866108117113995</v>
+        <v>-0.8736316693129353</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3887625967317518</v>
+        <v>-0.3756517923568126</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3116730082262791</v>
+        <v>0.3247159045206445</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5723624343046083</v>
+        <v>0.5854286886050843</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7960253222243168</v>
+        <v>0.8092063315195546</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.253160151067924</v>
+        <v>1.266358890022687</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.209022300524744</v>
+        <v>1.222427428177575</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.176980547882465</v>
+        <v>1.190437841592683</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.153793181336127</v>
+        <v>1.167245470056237</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.194102761525365</v>
+        <v>1.207658807876967</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.271112522126352</v>
+        <v>1.260682886428199</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1600</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.05593832020997525</v>
+        <v>-0.0672709923664101</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.269988066825768</v>
+        <v>1.282897876401819</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3126193602291778</v>
+        <v>0.3256264916467799</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1196275071633224</v>
+        <v>-0.1066483647648582</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.7794512777645082</v>
+        <v>0.7925620821394475</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.264393215480169</v>
+        <v>1.277436111774534</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.804659498207883</v>
+        <v>1.817725752508359</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.087476099426389</v>
+        <v>2.100657108721627</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.651476213244088</v>
+        <v>2.664674952198851</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.488851028216153</v>
+        <v>2.502256155868984</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.534097703898581</v>
+        <v>2.547554997608799</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.380980861244019</v>
+        <v>2.394433149964129</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.835726250299111</v>
+        <v>2.849282296650713</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.897947582575398</v>
+        <v>2.887517946877246</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1462</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.03734143355199393</v>
+        <v>0.02600876139555908</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.914139913611002</v>
+        <v>1.927049723187054</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6300783205574945</v>
+        <v>0.6430854519750966</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4183341891431098</v>
+        <v>0.431313331541574</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.316301482962871</v>
+        <v>1.32941228733781</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.955740684700416</v>
+        <v>1.968783580994781</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.076205325841265</v>
+        <v>2.089271580141741</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.703413171929803</v>
+        <v>2.716594181225041</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.326407813791285</v>
+        <v>3.339606552746048</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.228676609611512</v>
+        <v>3.242081737264343</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.434320002120188</v>
+        <v>3.447777295830406</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.605502065074383</v>
+        <v>3.618954353794493</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.211239246195142</v>
+        <v>4.224795292546744</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.324161672862679</v>
+        <v>4.313732037164527</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1324</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.3766523142311158</v>
+        <v>0.3653196420746809</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.937284139333329</v>
+        <v>1.95019394890938</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.164771928205006</v>
+        <v>1.177779059622608</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7663241544681014</v>
+        <v>0.7793032968665656</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.662948256616467</v>
+        <v>1.676059060991406</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.715677203395572</v>
+        <v>2.728720099689937</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.782000887935986</v>
+        <v>2.795067142236462</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.994575797311583</v>
+        <v>3.007756806606821</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.839920322005419</v>
+        <v>3.853119060960182</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.896139547853615</v>
+        <v>3.909544675506446</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.993501027161422</v>
+        <v>4.00695832087164</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.254470287225885</v>
+        <v>4.267922575945995</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.816088788063468</v>
+        <v>4.82964483441507</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.763695316714369</v>
+        <v>4.753265681016217</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1187</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2445566250301212</v>
+        <v>0.2332239528736864</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.328854958148426</v>
+        <v>1.341764767724477</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.186724246497079</v>
+        <v>1.199731377914681</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.9799933858442529</v>
+        <v>0.9929725282427171</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.536770148868129</v>
+        <v>1.549880953243068</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.339688076474268</v>
+        <v>2.352730972768633</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.254954359201989</v>
+        <v>2.268020613502465</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.293246950310966</v>
+        <v>2.306427959606204</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.990461048964391</v>
+        <v>3.003659787919155</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.898549848772184</v>
+        <v>2.911954976425015</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.862288521084764</v>
+        <v>2.875745814794982</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.065163675060354</v>
+        <v>3.078615963780464</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.487369047266249</v>
+        <v>3.500925093617852</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.568598382912377</v>
+        <v>3.558168747214225</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1048</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.08289755765261475</v>
+        <v>0.0715648854961799</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.761400280566221</v>
+        <v>0.7743100901422721</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.9390506579391058</v>
+        <v>0.9520577893567079</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2105251645923971</v>
+        <v>0.2235043069908613</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.007981812115652</v>
+        <v>1.021092616490591</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.973362681129025</v>
+        <v>1.98640557742339</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.697789269200257</v>
+        <v>1.710855523500733</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.612285259731728</v>
+        <v>1.625466269026965</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.028384610190649</v>
+        <v>2.041583349145412</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.082839577834484</v>
+        <v>1.096244705487315</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.259765642829876</v>
+        <v>1.273222936540094</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.294148800175307</v>
+        <v>1.307601088895417</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.828092662512844</v>
+        <v>1.841648708864447</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.791554452804412</v>
+        <v>1.78112481710626</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>911</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1959140398339301</v>
+        <v>0.1845813676774952</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.218808044871878</v>
+        <v>1.231717854447929</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.250942631359798</v>
+        <v>2.263949762777401</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.06396195496621</v>
+        <v>1.076941097364674</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.733005064811707</v>
+        <v>1.746115869186646</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.579294422944493</v>
+        <v>2.592337319238858</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.494560705672214</v>
+        <v>2.50762695997269</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.015302663641542</v>
+        <v>3.02848367293678</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.393380713792936</v>
+        <v>3.4065794527477</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.104177592431313</v>
+        <v>2.117582720084144</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.448271688530852</v>
+        <v>2.46172898224107</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.811963298126557</v>
+        <v>2.825415586846667</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.269864559849054</v>
+        <v>3.283420606200657</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.751199503541365</v>
+        <v>2.740769867843213</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>774</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2970558912694088</v>
+        <v>-0.3083885634258436</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.6753498239317111</v>
+        <v>0.6882596335077622</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.572470781417806</v>
+        <v>1.585477912835408</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.9275301155756921</v>
+        <v>0.9405092579741563</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.293501665361404</v>
+        <v>1.306612469736343</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.10773946871015</v>
+        <v>2.120782365004516</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.2814036842544</v>
+        <v>2.294469938554876</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.364607882372127</v>
+        <v>3.377788891667365</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.078801794639439</v>
+        <v>4.092000533594202</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.841079710386708</v>
+        <v>2.854484838039539</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.282321218110468</v>
+        <v>3.295778511820686</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.091898173905513</v>
+        <v>4.105350462625623</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.70523529422676</v>
+        <v>4.718791340578363</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.050563861645159</v>
+        <v>4.040134225947007</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>635</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.15223097112861</v>
+        <v>2.140898298972175</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.745381767613175</v>
+        <v>2.758291577189226</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.767835895662245</v>
+        <v>3.780843027079847</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.268167768427233</v>
+        <v>3.281146910825697</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.359667813197575</v>
+        <v>3.372778617572514</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.129550695795125</v>
+        <v>4.14259359208949</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.832218553325994</v>
+        <v>4.84528480762647</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.782357989190167</v>
+        <v>5.795538998485405</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.351279362850384</v>
+        <v>6.364478101805148</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.028713232940575</v>
+        <v>5.042118360593406</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.768841798386767</v>
+        <v>5.782299092096984</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.905587160456612</v>
+        <v>6.919039449176722</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.115253809354229</v>
+        <v>7.128809855705832</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.207494826669894</v>
+        <v>7.197065190971742</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>498</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.731461278183602</v>
+        <v>3.720128606027167</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.533542283693237</v>
+        <v>5.546452093269288</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.544296067056493</v>
+        <v>6.557303198474095</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.666517071149933</v>
+        <v>4.679496213548397</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.734521558889007</v>
+        <v>5.747632363263946</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.031963496604668</v>
+        <v>6.045006392899033</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.152049056440823</v>
+        <v>7.165115310741299</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.692897786173369</v>
+        <v>8.706078795468606</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10.03752038995092</v>
+        <v>10.05071912890568</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.584985566368772</v>
+        <v>8.598390694021603</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.384248306308208</v>
+        <v>9.397705600018426</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.20319612981718</v>
+        <v>10.21675217616878</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.85050782353926</v>
+        <v>9.840078187841108</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>360</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.173228346456689</v>
+        <v>4.161895674300254</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.061654733492432</v>
+        <v>5.074564543068483</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.055674915784728</v>
+        <v>6.06868204720233</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.925284611097837</v>
+        <v>5.938395415472776</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.66717099325794</v>
+        <v>5.680213889552306</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.693548387096783</v>
+        <v>6.706614641397259</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.448587210537497</v>
+        <v>8.461768219832734</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.554253991021866</v>
+        <v>7.56745272997663</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.704128805993939</v>
+        <v>6.71753393364677</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.888264370565253</v>
+        <v>7.90172166427547</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.033758639021798</v>
+        <v>9.047210927741908</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.446837361410225</v>
+        <v>9.460393407761828</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.141003138130955</v>
+        <v>9.130573502432803</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>222</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.61466978789813</v>
+        <v>5.603337115741695</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.705798877636582</v>
+        <v>6.718708687212633</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.112731972841793</v>
+        <v>8.125739104259395</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.342084204548392</v>
+        <v>7.355063346946856</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.85771704353029</v>
+        <v>10.87082784790523</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.902906728993678</v>
+        <v>8.915949625288043</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.367722561270952</v>
+        <v>8.380788815571428</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.900539162489451</v>
+        <v>7.913720171784689</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.938638375406249</v>
+        <v>6.951837114361012</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.638062739927875</v>
+        <v>5.651467867580706</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.136012118312991</v>
+        <v>8.149469412023208</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.719944825207975</v>
+        <v>7.733397113928085</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.299690214263073</v>
+        <v>7.313246260614676</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.549411546539361</v>
+        <v>7.538981910841208</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.9794</t>
+          <t>X &gt; 0.9793</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.458942632170981</v>
+        <v>3.447609960014546</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.404881264991083</v>
+        <v>7.417888396408685</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-2.781571519621224</v>
+        <v>-2.768390510325986</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2.842571405803525</v>
+        <v>-2.829372666848762</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.087926105625229</v>
+        <v>-5.074468811915011</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-7.854749940177079</v>
+        <v>-7.841193893825476</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-7.605028607900792</v>
+        <v>-7.615458243598944</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Cycle Phase is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Cycle Phase is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.50477099236641</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.118928258818435</v>
+        <v>-2.105921127400833</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.717572531759302</v>
+        <v>-3.704461727384363</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.8858166922683</v>
+        <v>-5.872750437967824</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.972047710097421</v>
+        <v>-3.958866700802183</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.17590473913687</v>
+        <v>-11.16270600018211</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.645077543212409</v>
+        <v>-9.631672415559578</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.42125943895856</v>
+        <v>-13.40780214524835</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.19640009113694</v>
+        <v>-12.18294780241683</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-10.23570232112946</v>
+        <v>-10.22214627477786</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.985980988853171</v>
+        <v>-9.996410624551324</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>227</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.475817174835527</v>
+        <v>-4.487149846991962</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.563161712909917</v>
+        <v>-2.550251903333866</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.363316763118839</v>
+        <v>-7.350309631701236</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-11.63834997412368</v>
+        <v>-11.62537083172521</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.41465665175091</v>
+        <v>-10.40154584737597</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.43880061711895</v>
+        <v>-11.42575772082458</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-12.84512023747493</v>
+        <v>-12.83205398317445</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-11.99071773317273</v>
+        <v>-11.97753672387749</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.69488942552243</v>
+        <v>-14.68169068656767</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-13.34237143874419</v>
+        <v>-13.32896631109136</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-13.10659612870054</v>
+        <v>-13.09313883499032</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-14.39379887443881</v>
+        <v>-14.3803465857187</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.17088167921631</v>
+        <v>-12.1573256328647</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.956402637688917</v>
+        <v>-7.96683227338707</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>369</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.00292341506092</v>
+        <v>-1.014256087217355</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.09553007224581478</v>
+        <v>0.1084398818218659</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.738363024594669</v>
+        <v>-2.725355893177067</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.692120732095574</v>
+        <v>-3.67914158969711</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.9785094268425354</v>
+        <v>-0.9653986224675961</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.849089169343678</v>
+        <v>-2.836046273049313</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.933822886615957</v>
+        <v>-2.920756632315481</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.859000865343262</v>
+        <v>-2.845819856048024</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.088022431742367</v>
+        <v>-5.074823692787604</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.228120516499288</v>
+        <v>-3.214715388846457</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.245881970898161</v>
+        <v>-4.232424677187943</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.024506943634037</v>
+        <v>-5.011054654913927</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.089748004443443</v>
+        <v>-4.07619195809184</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.485013122031646</v>
+        <v>-2.495442757729798</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>512</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.412811679790025</v>
+        <v>1.40147900763359</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.144988066825768</v>
+        <v>2.157897876401819</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.164181860229178</v>
+        <v>1.17718899164678</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5131849928366776</v>
+        <v>0.5261641352351418</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.904451277764508</v>
+        <v>2.917562082139447</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.444080715480169</v>
+        <v>1.457123611774534</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.14059699820789</v>
+        <v>2.153663252508366</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.064038599426389</v>
+        <v>2.077219608721627</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.612413713244088</v>
+        <v>1.625612452198851</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.30135102821616</v>
+        <v>3.314756155868992</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.705972703898581</v>
+        <v>2.719429997608799</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.349730861244012</v>
+        <v>2.363183149964122</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.491976250299111</v>
+        <v>3.505532296650713</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.499510082575398</v>
+        <v>5.489080446877246</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>654</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3.011148835753325</v>
+        <v>2.99981616359689</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.693153204440442</v>
+        <v>3.706063014016493</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.757000094174124</v>
+        <v>3.770007225591726</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.887253226781624</v>
+        <v>3.900232369180088</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.183694397030557</v>
+        <v>5.196805201405496</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.563705142085674</v>
+        <v>4.576748038380039</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.937687021143667</v>
+        <v>4.950753275444143</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.23502961624596</v>
+        <v>5.248210625541198</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.326934928840423</v>
+        <v>5.340133667795186</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.229103321794142</v>
+        <v>7.242508449446973</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.788875991360356</v>
+        <v>7.802333285070574</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.976164347482552</v>
+        <v>7.989616636202662</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>9.543677320635503</v>
+        <v>9.557233366987106</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>10.8637350443491</v>
+        <v>10.85330540865095</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>797</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.717352144030926</v>
+        <v>3.706019471874491</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.987836247503303</v>
+        <v>4.000746057079354</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.969379084194053</v>
+        <v>3.982386215611655</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.726984788947092</v>
+        <v>4.739963931345557</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.945150775882446</v>
+        <v>5.958261580257386</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.113358083736131</v>
+        <v>5.126400980030496</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.028624366463852</v>
+        <v>5.041690620764328</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.43973456868612</v>
+        <v>5.452915577981358</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.127793653645597</v>
+        <v>5.14099239260036</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>6.410667213912525</v>
+        <v>6.424072341565356</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.209678005027818</v>
+        <v>7.223135298738036</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7.620472705660575</v>
+        <v>7.633924994380685</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.956805296723196</v>
+        <v>8.970361343074799</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>10.58670228771969</v>
+        <v>10.57627265202154</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>939</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.523601083410895</v>
+        <v>3.51226841125446</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.106915649360374</v>
+        <v>5.119825458936425</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.81854321539425</v>
+        <v>4.831550346811852</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.694270256414953</v>
+        <v>5.707249398813417</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.327308040277821</v>
+        <v>6.34041884465276</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.879276069580278</v>
+        <v>5.892318965874644</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.581549807047082</v>
+        <v>5.594616061347558</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.966336589309243</v>
+        <v>5.979517598604481</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.05336652208328</v>
+        <v>5.066565261038043</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.013677971773134</v>
+        <v>6.027083099425965</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.4479022832383</v>
+        <v>6.461359576948517</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.801774258475113</v>
+        <v>6.815226547195223</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>7.87246746435661</v>
+        <v>7.886023510708213</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>8.974158977676566</v>
+        <v>8.963729341978414</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>1081</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.195738368041646</v>
+        <v>3.184405695885211</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.636893709748989</v>
+        <v>4.64980351932504</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.167094383355909</v>
+        <v>5.180101514773511</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.482361392004115</v>
+        <v>5.49534053440258</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.239037309216869</v>
+        <v>6.252148113591808</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.611409866729012</v>
+        <v>5.624452763023378</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.341662273416027</v>
+        <v>5.354728527716503</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.614534378797345</v>
+        <v>5.627715388092582</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.27601367855398</v>
+        <v>5.289212417508743</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.091013377892388</v>
+        <v>6.104418505545219</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.441301681696913</v>
+        <v>6.454758975407131</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.475684839042344</v>
+        <v>6.489137127762454</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.258020422362023</v>
+        <v>7.271576468713626</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>7.785262568699352</v>
+        <v>7.7748329330012</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>1225</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.690235149177774</v>
+        <v>2.678902477021339</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.609273781111483</v>
+        <v>3.622183590687534</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.030731605127137</v>
+        <v>4.043738736544739</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.569148003040759</v>
+        <v>4.582127145439223</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.826645155315525</v>
+        <v>5.839755959690464</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.899597297112827</v>
+        <v>4.912640193407192</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.38629215126911</v>
+        <v>5.399358405569586</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.164006711671291</v>
+        <v>5.177187720966529</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.939741519366535</v>
+        <v>4.952940258321298</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.559004089440648</v>
+        <v>5.57240921709348</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>6.088944642674093</v>
+        <v>6.102401936384311</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.123327800019524</v>
+        <v>6.136780088739634</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.601032372748094</v>
+        <v>6.614588419099697</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.095651664208049</v>
+        <v>7.085222028509897</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>1366</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.557806189306866</v>
+        <v>2.546473517150432</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.288838725683746</v>
+        <v>3.301748535259797</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.626034440756271</v>
+        <v>3.639041572173873</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.707971321533599</v>
+        <v>4.720950463932063</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.267646738965091</v>
+        <v>5.28075754334003</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.686611370677831</v>
+        <v>4.699654266972196</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.114322748573919</v>
+        <v>5.127389002874395</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>5.013171560626972</v>
+        <v>5.02635256992221</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.318203885279225</v>
+        <v>5.331402624233988</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.785794659255693</v>
+        <v>5.799199786908524</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>6.313105756607214</v>
+        <v>6.326563050317432</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.493901798286473</v>
+        <v>6.507354087006583</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6.952124493344499</v>
+        <v>6.965680539696102</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.42146515212152</v>
+        <v>7.411035516423368</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>1509</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.178529870644894</v>
+        <v>2.167197198488459</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.820104037667392</v>
+        <v>2.833013847243443</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.485540168711616</v>
+        <v>3.498547300129218</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.212214772492082</v>
+        <v>4.225193914890546</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.932905552118385</v>
+        <v>4.946016356493324</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.766464123366191</v>
+        <v>4.779507019660556</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.278151877266872</v>
+        <v>5.291218131567348</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.341120897305778</v>
+        <v>5.354301906601016</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.478928168181127</v>
+        <v>5.492126907135891</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.622838768441476</v>
+        <v>5.636243896094307</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5.948237862944303</v>
+        <v>5.961695156654521</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.512773439110148</v>
+        <v>6.526225727830258</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.02028556110097</v>
+        <v>7.033841607452572</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7.468814050434915</v>
+        <v>7.458384414736763</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1652</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.470242067199223</v>
+        <v>2.458909395042788</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.098377897334245</v>
+        <v>3.111287706910296</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.793097568461626</v>
+        <v>3.806104699879228</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.589210265233774</v>
+        <v>4.602189407632238</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.958779364931573</v>
+        <v>4.971890169306512</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.590361738482585</v>
+        <v>4.60340463477695</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5.171487585374955</v>
+        <v>5.184553839675431</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.067500312501451</v>
+        <v>5.080681321796689</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.067033113970474</v>
+        <v>5.080231852925237</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.306496306666517</v>
+        <v>5.319901434319348</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.464939108256935</v>
+        <v>5.478396401967153</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.923051079161688</v>
+        <v>5.936503367881798</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.35025409533543</v>
+        <v>6.363810141687033</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.539442739960386</v>
+        <v>6.529013104262233</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1793</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.773153983192145</v>
+        <v>1.76182131103571</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.890526270952925</v>
+        <v>1.903436080528977</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.611106532566048</v>
+        <v>2.62411366398365</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.964449458815487</v>
+        <v>2.977428601213951</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.151070073079623</v>
+        <v>3.164180877454562</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.611925284638005</v>
+        <v>2.62496818093237</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.029143603060092</v>
+        <v>3.042209857360568</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.561960204278591</v>
+        <v>2.575141213573829</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.222098076043864</v>
+        <v>2.235296814998627</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.487421859225634</v>
+        <v>2.500826986878465</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.561530776960495</v>
+        <v>2.574988070670713</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.320955763642225</v>
+        <v>3.334408052362335</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.569970533623142</v>
+        <v>3.583526579974745</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.708146969078463</v>
+        <v>3.697717333380311</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>1936</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.380528621938794</v>
+        <v>1.369195949782359</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.215236000710057</v>
+        <v>1.228145810286108</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.646813575105213</v>
+        <v>1.659820706522815</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.725413815150731</v>
+        <v>1.738392957549195</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.755174418260374</v>
+        <v>1.768285222635313</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.174517182422321</v>
+        <v>1.187560078716686</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.606312390769872</v>
+        <v>1.619378645070348</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.242434777112337</v>
+        <v>1.255615786407574</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8198646429961514</v>
+        <v>0.8330633819509146</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7961857389599629</v>
+        <v>0.809590866612794</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.9013497700142921</v>
+        <v>0.9148070637245098</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.348956067855589</v>
+        <v>1.362408356575699</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.393577489968536</v>
+        <v>1.407133536320138</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.488340144558862</v>
+        <v>1.47791050886071</v>
       </c>
     </row>
     <row r="20">
@@ -4639,46 +4639,46 @@
         <v>2079</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.138115311343654</v>
+        <v>1.126782639187219</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9214430932807929</v>
+        <v>0.934352902856844</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.488575348685167</v>
+        <v>1.501582480102769</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.57072843319262</v>
+        <v>1.583707575591085</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.465207651020883</v>
+        <v>1.478318455395822</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.8968487229356725</v>
+        <v>0.9098916192300379</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.245015438563833</v>
+        <v>1.258081692864309</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8259320878823786</v>
+        <v>0.8391130971776164</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6206320573999307</v>
+        <v>0.6338307963546939</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6363077381728743</v>
+        <v>0.6497128658257054</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7201547024555879</v>
+        <v>0.7336119961658056</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.187438292701444</v>
+        <v>1.200890581421554</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.151984066556935</v>
+        <v>1.165540112908538</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.01690501403283</v>
+        <v>1.006475378334677</v>
       </c>
     </row>
     <row r="21">
@@ -4691,46 +4691,46 @@
         <v>2221</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.131055151199298</v>
+        <v>1.119722479042863</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.5550511014948398</v>
+        <v>0.567960911070891</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.060677667298066</v>
+        <v>1.073684798715668</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.190930799905566</v>
+        <v>1.20390994230403</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.147781984653292</v>
+        <v>1.160892789028232</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5447286499691444</v>
+        <v>0.5577715462635098</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6400939871768259</v>
+        <v>0.6531602414773019</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3079848792553008</v>
+        <v>0.3211658885505386</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.06818835226693665</v>
+        <v>-0.05498961331217345</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.06284302851504719</v>
+        <v>-0.04943790086221611</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.0424725347326671</v>
+        <v>-0.02901524102244935</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1269849134727394</v>
+        <v>0.1404372021928495</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.06692841148776552</v>
+        <v>0.08048445783936842</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.001476398424117065</v>
+        <v>-0.008953237274035075</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6275807880702757</v>
+        <v>0.6361458157829958</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1967706417553785</v>
+        <v>-0.2067518051268422</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.3662477070205128</v>
+        <v>0.3559472223179725</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5623452819523251</v>
+        <v>0.5519789195530294</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3450350718946638</v>
+        <v>0.3346539188741389</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2701812526049352</v>
+        <v>-0.2802521060051291</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3317815405320061</v>
+        <v>-0.341848715576738</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5202751782567461</v>
+        <v>-0.5303560883835203</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.856246411383097</v>
+        <v>-0.8662023902202307</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6601792360634633</v>
+        <v>-0.6703844491587034</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5427946201952309</v>
+        <v>-0.5530950450169527</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.3993092411450618</v>
+        <v>-0.4096713276478212</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4116062294277327</v>
+        <v>-0.4220487613697657</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6502484037610685</v>
+        <v>-0.6417981009247171</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3590474173613316</v>
+        <v>0.3669194353321572</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4156519657873616</v>
+        <v>-0.4246204610064908</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3940834711590284</v>
+        <v>0.3847123049366274</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.628332509156543</v>
+        <v>0.618881814680492</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.275624747152257</v>
+        <v>0.2662207928697669</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2210600307427768</v>
+        <v>-0.2302169494499609</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4061248155176074</v>
+        <v>-0.4152264728897634</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5650576153263671</v>
+        <v>-0.5741794925855643</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.8899178995931933</v>
+        <v>-0.8989233314137408</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.8589250454034669</v>
+        <v>-0.868093394417194</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.8365037690965096</v>
+        <v>-0.8457220985057248</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.8203597036352335</v>
+        <v>-0.8295848533092069</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.849367934795076</v>
+        <v>-0.8586587594278825</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.9045155472894066</v>
+        <v>-0.8967265248672192</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.03454315412425046</v>
+        <v>0.04152530392988041</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.784548612710914</v>
+        <v>-0.7922179090092172</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1931985231234705</v>
+        <v>-0.2011592226389354</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.07395827336218019</v>
+        <v>0.06590860703892076</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4820726882192616</v>
+        <v>-0.4899920136874485</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7823005200186728</v>
+        <v>-0.7900648545957765</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.117003944732154</v>
+        <v>-1.124656304722883</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.292554860325929</v>
+        <v>-1.300213297467934</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.642416547112092</v>
+        <v>-1.649953530773288</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.542277941574696</v>
+        <v>-1.549984455822838</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.570924574288171</v>
+        <v>-1.578655304482602</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.476577278290875</v>
+        <v>-1.484344455615116</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.759271810964947</v>
+        <v>-1.766996773116723</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.798571036509166</v>
+        <v>-1.791403146569827</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.02000482808831805</v>
+        <v>-0.01392850152391389</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.025833047543735</v>
+        <v>-1.032373285195838</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3377977648166564</v>
+        <v>-0.344644769350289</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2243597155272212</v>
+        <v>-0.2312358235107297</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7062138598501662</v>
+        <v>-0.7129863404577677</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.049666990099858</v>
+        <v>-1.056279484555745</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.114730880051383</v>
+        <v>-1.121334453071661</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.452016920411971</v>
+        <v>-1.458560665791772</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.787287109063882</v>
+        <v>-1.793719610622603</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.735413677666195</v>
+        <v>-1.741978500507336</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.846625907723336</v>
+        <v>-1.853180296508853</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.939383377166585</v>
+        <v>-1.945903370815579</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.266040404099122</v>
+        <v>-2.272498424467756</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.327659928470261</v>
+        <v>-2.321191107226539</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1739405873882163</v>
+        <v>-0.168648258754132</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8949630846047967</v>
+        <v>-0.9006127618960562</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5382750551285866</v>
+        <v>-0.5440961182624946</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3542643786717008</v>
+        <v>-0.3601387661610218</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7690337030248671</v>
+        <v>-0.7748261860169734</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.256309090599494</v>
+        <v>-1.261901995106363</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.287441165895572</v>
+        <v>-1.293035952592959</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.386300124349837</v>
+        <v>-1.391915418366807</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.77826320613331</v>
+        <v>-1.783751621227715</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.804929587599091</v>
+        <v>-1.810506173616844</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.850680910032111</v>
+        <v>-1.856267605610235</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.972310455282603</v>
+        <v>-1.977854214404097</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.233450632362889</v>
+        <v>-2.238952997466939</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.209927329828247</v>
+        <v>-2.20431655399841</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2991</v>
+        <v>2992</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.09663405922461976</v>
+        <v>-0.09212540168421413</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5252583534206607</v>
+        <v>-0.530184680189393</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4692344039280485</v>
+        <v>-0.4742194956992023</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3876215091626491</v>
+        <v>-0.3926243807541994</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6080487222354876</v>
+        <v>-0.6130318865376623</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9260452640129984</v>
+        <v>-0.9308972215588014</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8928054784432149</v>
+        <v>-0.8976793825366514</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9082696463193614</v>
+        <v>-0.9131854529861769</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.18480549570117</v>
+        <v>-1.189637693780455</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.148774180464969</v>
+        <v>-1.153701788056239</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.13478172161912</v>
+        <v>-1.139736321255974</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.215619539691509</v>
+        <v>-1.220546809955714</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.383525086599278</v>
+        <v>-1.388439053165527</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.4162240991364</v>
+        <v>-1.411613069165533</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.02764131098312106</v>
+        <v>-0.0238549618320576</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2539616467324706</v>
+        <v>-0.2581854834454589</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3133158514868342</v>
+        <v>-0.3175546031972729</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.07026444983847568</v>
+        <v>-0.07457259271773609</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3365291300086639</v>
+        <v>-0.3407977904720099</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6590452803770646</v>
+        <v>-0.6631898837654475</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5671925897742582</v>
+        <v>-0.5713755859237608</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5387994107776919</v>
+        <v>-0.5430311284476446</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6822638233113523</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3620982378974347</v>
+        <v>-0.36646393982479</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4213962316264741</v>
+        <v>-0.4257618498704545</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.4330357415656962</v>
+        <v>-0.4373973639203328</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6118943182093517</v>
+        <v>-0.6162349447286033</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5998559318015992</v>
+        <v>-0.5961733658024144</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.05441392996607419</v>
+        <v>-0.05125072415550136</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3386197404325486</v>
+        <v>-0.3421021235981812</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6255670339135975</v>
+        <v>-0.6289900072858288</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2957794754269756</v>
+        <v>-0.2992963208356301</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4819192961060708</v>
+        <v>-0.4854170145953702</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7174770135274642</v>
+        <v>-0.7208850115465921</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6941187546937613</v>
+        <v>-0.6975414230641519</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.8392730603658478</v>
+        <v>-0.8426843695923623</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.9447951803989483</v>
+        <v>-0.9481802265362589</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5860305064827003</v>
+        <v>-0.5895836974317419</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.682072020872063</v>
+        <v>-0.6856114652465948</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7836336997838274</v>
+        <v>-0.7871417735832793</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9115197717327206</v>
+        <v>-0.9150187128323068</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7671694973144128</v>
+        <v>-0.7640273407604568</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.06728746264047203</v>
+        <v>0.06983403981615055</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1530213008557268</v>
+        <v>-0.1559007773880623</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3563960131236783</v>
+        <v>-0.3592388479316782</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2102836290145191</v>
+        <v>-0.2131637381177143</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2933402546116923</v>
+        <v>-0.2962267286397022</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4781331620110407</v>
+        <v>-0.4809509377420227</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5176799916777739</v>
+        <v>-0.5204923014189475</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.7636969211014772</v>
+        <v>-0.7664639701408689</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9260758548110601</v>
+        <v>-0.9288001211149322</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6452452159152884</v>
+        <v>-0.6480995202823721</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.7456755570347866</v>
+        <v>-0.7485130775085764</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9298676413983884</v>
+        <v>-0.9326507948553697</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.069560093313228</v>
+        <v>-1.072326628775002</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.9210154021484485</v>
+        <v>-0.9183741236073359</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3543</v>
+        <v>3544</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3843269591301137</v>
+        <v>-0.3821957885429583</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.4903846476608678</v>
+        <v>-0.4925520673552057</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6732064698214728</v>
+        <v>-0.6753404563138332</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5840941550665093</v>
+        <v>-0.5862488149618201</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6006162898030567</v>
+        <v>-0.6027904368585766</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.7384580940101202</v>
+        <v>-0.7405819062434915</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.8643545862991502</v>
+        <v>-0.8664477197529692</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.034600541881026</v>
+        <v>-1.036666834940348</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.136714316631902</v>
+        <v>-1.138755591616309</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9002630118176711</v>
+        <v>-0.9024084439055358</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.033055426389069</v>
+        <v>-1.035173364387255</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.236966952578271</v>
+        <v>-1.239027086922519</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.274883230513538</v>
+        <v>-1.276951835930383</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.291775110057955</v>
+        <v>-1.28954187253585</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.5031864924276874</v>
+        <v>-0.5015224812673367</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.7463987154060874</v>
+        <v>-0.7479374878007263</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.882974652233564</v>
+        <v>-0.8844899763922243</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6297901087893436</v>
+        <v>-0.6313706622452102</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7741370930676936</v>
+        <v>-0.7756967254486256</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8145113398343682</v>
+        <v>-0.8160512831834481</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.9660212720660439</v>
+        <v>-0.9675237051922849</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.174460959716313</v>
+        <v>-1.17592276651569</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.356495292861744</v>
+        <v>-1.35791050629274</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.16051107818992</v>
+        <v>-1.162007751865069</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.268899173646901</v>
+        <v>-1.270373884041575</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.409689969826061</v>
+        <v>-1.411126176671772</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.380383502485465</v>
+        <v>-1.38184209226835</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.333030678294165</v>
+        <v>-1.331257521745414</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3818</v>
+        <v>3819</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3921592807946794</v>
+        <v>-0.3909922867296629</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4757691133308981</v>
+        <v>-0.4768580619954648</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5693504752370018</v>
+        <v>-0.5704244221913441</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.372762303401565</v>
+        <v>-0.3738852412339071</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5573824039705286</v>
+        <v>-0.5584697882889742</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5332413898517672</v>
+        <v>-0.5343289783744112</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.6299810246679201</v>
+        <v>-0.6310458104817016</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.7953690888581306</v>
+        <v>-0.7964017148077787</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7113605641558607</v>
+        <v>-0.7124170980103557</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6314721010355484</v>
+        <v>-0.6325692430323997</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7432020867321469</v>
+        <v>-0.7442751960071092</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.8513489816879272</v>
+        <v>-0.8523935969607663</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.8905109845791301</v>
+        <v>-0.8915553996843641</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.8619070533596442</v>
+        <v>-0.8606982091845552</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3956</v>
+        <v>3957</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3140480455816075</v>
+        <v>-0.3133352241044491</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3751732234968088</v>
+        <v>-0.3758007882492223</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4540021421655709</v>
+        <v>-0.454615443837092</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4109789948082962</v>
+        <v>-0.4116017300282735</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.6079226188307061</v>
+        <v>-0.6085032229538498</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4985987118659452</v>
+        <v>-0.4992032324877584</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4687444886707368</v>
+        <v>-0.4693580012756868</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4426854351521072</v>
+        <v>-0.4433121065193504</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3888860690078673</v>
+        <v>-0.3895274708198286</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3160732142080747</v>
+        <v>-0.3167447277462543</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4562249785969996</v>
+        <v>-0.4568641943103913</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4330034742789834</v>
+        <v>-0.4336484362950301</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4095353114901314</v>
+        <v>-0.4101921854109278</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4236525185368336</v>
+        <v>-0.4229603194861582</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.9794</t>
+          <t>X &lt; 0.9793</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.07074535697646667</v>
+        <v>-0.07049640619308661</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.0865024348790584</v>
+        <v>-0.0867454155387648</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1515249759462236</v>
+        <v>-0.1517541707984265</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.0567620100872972</v>
+        <v>-0.05701377280383468</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1432424828984225</v>
+        <v>-0.1434759295564589</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.07623330816683449</v>
+        <v>-0.07648175320230877</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.02302087348221704</v>
+        <v>0.02274769302518109</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.05698829454834708</v>
+        <v>0.05670441425686334</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.05825225618139029</v>
+        <v>0.05796763512568504</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1244964650146017</v>
+        <v>0.1241913839734039</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1043167666274059</v>
+        <v>0.1040154661300363</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1280511737440122</v>
+        <v>0.1277441092025882</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.161123075695933</v>
+        <v>0.1608057341507134</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1560386915153131</v>
+        <v>0.156214528073825</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/cycle/cycle_phase.xlsx
+++ b/workspaces/btc_daily_14days/cycle/cycle_phase.xlsx
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.0358</t>
+          <t>X ≈ 0.03582</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.632926298359571</v>
+        <v>-6.011389036481035</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.520120032838761</v>
+        <v>-6.88962419232633</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.40185699892339</v>
+        <v>-10.79500303801311</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.85476598766358</v>
+        <v>-16.28767803407114</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.30275262803059</v>
+        <v>-14.67208193191318</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-18.19709810438142</v>
+        <v>-18.62055477399405</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-16.88990713867506</v>
+        <v>-17.27960658419713</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-16.66238417737939</v>
+        <v>-17.04601416119577</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.7273341147834</v>
+        <v>-16.38369986392642</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-15.48493050081679</v>
+        <v>-15.1003743051688</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-12.89830179835705</v>
+        <v>-13.19710233437629</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-15.66307322488116</v>
+        <v>-15.25397024401789</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-13.29065828088127</v>
+        <v>-12.83676169829833</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.774632402772788</v>
+        <v>-6.957208645669091</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.0689</t>
+          <t>X ≈ 0.06893</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>142</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.522926510860628</v>
+        <v>4.517644173807689</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.345375850778126</v>
+        <v>4.344229683643022</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.655829597841127</v>
+        <v>4.655708424834643</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.001754880637449</v>
+        <v>9.001319758923586</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.0872776648524</v>
+        <v>14.13579063887553</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.87393669221075</v>
+        <v>10.89789903693462</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12.90100870580484</v>
+        <v>12.94898806776476</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.73466756021082</v>
+        <v>11.78388051843482</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.27025996909424</v>
+        <v>10.34344838727545</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.94105722434506</v>
+        <v>13.0403292570756</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.925014848201727</v>
+        <v>10.02485916129106</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.961820321261364</v>
+        <v>10.0854611268819</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.840103042665206</v>
+        <v>8.98875710258168</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.251074284905101</v>
+        <v>6.423073044472396</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>143</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.608463197217596</v>
+        <v>7.603221347962538</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.422037059162307</v>
+        <v>7.420927107109577</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.2145411646372</v>
+        <v>11.21448397979421</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.34764123719373</v>
+        <v>11.34723485604424</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.90578389711641</v>
+        <v>12.95429306275421</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.50861218270379</v>
+        <v>12.53259052839125</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>15.2192823276136</v>
+        <v>15.26727758569393</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.75703162638505</v>
+        <v>14.80626071092725</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>18.89046098633644</v>
+        <v>18.96368206590125</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>20.1419006580885</v>
+        <v>20.24119329721027</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>20.64157997864027</v>
+        <v>20.74144723511361</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.38041434673001</v>
+        <v>21.50407055944004</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23.06338020536792</v>
+        <v>23.21204360991198</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>26.09250046435977</v>
+        <v>26.26449922392643</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>142</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.729920085380371</v>
+        <v>8.724705676220012</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.255648640528761</v>
+        <v>9.254570309693243</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.07743988895283</v>
+        <v>13.0774166993893</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>16.02023153669099</v>
+        <v>16.01988087540995</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13.37972271936766</v>
+        <v>13.42824057402631</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>15.7886781390328</v>
+        <v>15.81268797182882</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>15.00564117355282</v>
+        <v>15.05364095095489</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>16.6528049642723</v>
+        <v>16.70204853298623</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>18.70648139734276</v>
+        <v>18.77970506746815</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>21.37975955642659</v>
+        <v>21.47905759220166</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>26.10687969171846</v>
+        <v>26.20676228105484</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>28.26025410955376</v>
+        <v>28.38392206821676</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>31.36841365527337</v>
+        <v>31.51708383489812</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>30.19473625673624</v>
+        <v>30.36673501630323</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>143</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.907106867699852</v>
+        <v>6.901889366327275</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.327124196805649</v>
+        <v>5.326018768754324</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.935365674769187</v>
+        <v>4.935279061439033</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.552991267039992</v>
+        <v>8.552593717663768</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.413117453575843</v>
+        <v>9.461608417098823</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.620169067104385</v>
+        <v>7.644130689926115</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.444419761480013</v>
+        <v>5.492362802607786</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.376082328439118</v>
+        <v>6.425274423968865</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.222529054305788</v>
+        <v>4.295687926793086</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.676262140716524</v>
+        <v>2.775491172711028</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.568880031687236</v>
+        <v>4.668704754420986</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.00276945173318</v>
+        <v>6.126396786622358</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.283963024385798</v>
+        <v>6.432610007242189</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>9.309283681143135</v>
+        <v>9.481282440709485</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>142</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.411639344817274</v>
+        <v>2.406380327021616</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.35531932962616</v>
+        <v>11.35430259972056</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.561994083295325</v>
+        <v>9.561971707388821</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.09861697181164</v>
+        <v>11.09826253464263</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.457959458407949</v>
+        <v>8.506444859451236</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.16309855044892</v>
+        <v>10.18708768120565</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.676699858679186</v>
+        <v>8.724664383598565</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.916277054700238</v>
+        <v>8.965484056738383</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.639802817929649</v>
+        <v>4.712957556925595</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.792362360992726</v>
+        <v>3.891587104832695</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.182163986917338</v>
+        <v>2.281975528782468</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.217658609053565</v>
+        <v>2.34127328934207</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.798779082515487</v>
+        <v>1.947418361352419</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.08695388410882998</v>
+        <v>0.08504487545799577</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>142</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.007872149082516</v>
+        <v>1.002604071962729</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.530047857242423</v>
+        <v>1.528927179251646</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.453537336268589</v>
+        <v>7.453512010234441</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.075577701264066</v>
+        <v>4.075168252527902</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.64671462142018</v>
+        <v>5.695174554342231</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.838828384633338</v>
+        <v>3.862771853202034</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.756286866807294</v>
+        <v>3.804214741868641</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.291636248610232</v>
+        <v>3.340807198879347</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.748248430692477</v>
+        <v>6.821408777131417</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.605031840565545</v>
+        <v>6.704260355072556</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.403099103986861</v>
+        <v>6.502917452604486</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.328744561607159</v>
+        <v>4.452357383962926</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.206664648464162</v>
+        <v>3.355301335707459</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.08695388410851024</v>
+        <v>0.08504487545799577</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>144</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.115841025164819</v>
+        <v>-1.121133603167543</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.082085059898731</v>
+        <v>-4.083279457029157</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.476909507847751</v>
+        <v>-4.47707549223675</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.272093813105059</v>
+        <v>-2.272567924252023</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.72900901606652</v>
+        <v>2.777435581167595</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.435020422513233</v>
+        <v>-0.4111159930357644</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.716428751941095</v>
+        <v>5.764370105533366</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.787490043460494</v>
+        <v>1.836645793325353</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.421346571368197</v>
+        <v>2.494475228604955</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.573633628391946</v>
+        <v>1.6728293232648</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.451486836032309</v>
+        <v>3.551288307654012</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.487761948447002</v>
+        <v>3.611366042683571</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.681187845572296</v>
+        <v>1.829818156941911</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.908351280210738</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>141</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.384428719468616</v>
+        <v>1.379185774524991</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5092725895202648</v>
+        <v>0.508149460608422</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1160686212593092</v>
+        <v>0.1159671416453847</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.899335717519705</v>
+        <v>5.898975926952353</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4151582208281184</v>
+        <v>0.4635499123635114</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.83540279436707</v>
+        <v>2.859339641129075</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.752127107235758</v>
+        <v>2.800039790971987</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.703436038467046</v>
+        <v>3.752601424053317</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.600530433344176</v>
+        <v>8.673691699396791</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>7.755234193266638</v>
+        <v>7.854450772479879</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.262554158426042</v>
+        <v>8.362367134175727</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9.718162351808836</v>
+        <v>9.84177589256921</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>10.01141519031641</v>
+        <v>10.16005161973862</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.24168461354375</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>143</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.454730064206409</v>
+        <v>-1.460014135054841</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.644334809049447</v>
+        <v>-1.645487044092334</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.140413009964412</v>
+        <v>2.140354122287519</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5171135122554418</v>
+        <v>-0.5175452754080183</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.7339576175074</v>
+        <v>1.782355141978563</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5.518941543753648</v>
+        <v>5.542915133549108</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.831764743398871</v>
+        <v>6.879716137944513</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.462530531264711</v>
+        <v>8.51173644229565</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.009471234132391</v>
+        <v>7.082618411061453</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.069307060389526</v>
+        <v>4.168493423042904</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.470090129424072</v>
+        <v>2.569871389578793</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.69911267476612</v>
+        <v>6.822711951294401</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.680803503566779</v>
+        <v>7.829432706031362</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.910682282541579</v>
+        <v>8.082681042108241</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>143</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5.502608666810616</v>
+        <v>5.49748476245334</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6.011641161971816</v>
+        <v>6.010649527178309</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.012491029731137</v>
+        <v>7.012542115885417</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.537216105617894</v>
+        <v>8.536949301163716</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.216421520811608</v>
+        <v>5.264863016414047</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.727931320879684</v>
+        <v>2.751879973284595</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.039532574047449</v>
+        <v>4.087455709946028</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.180967165552737</v>
+        <v>2.230115889280896</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7261639404662219</v>
+        <v>0.7992537718208652</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.973555561888581</v>
+        <v>2.072714508370666</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3739721240095761</v>
+        <v>0.4737313916749812</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2891990402341875</v>
+        <v>-0.1656310584238909</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.707954146914723</v>
+        <v>-0.5593440925049649</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.278128906269608</v>
+        <v>-3.106130146703102</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>141</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.379435663078539</v>
+        <v>-6.384810706295376</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-12.19696899994176</v>
+        <v>-12.19833615932883</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-11.18432136230004</v>
+        <v>-11.18460812687665</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-16.00426015820277</v>
+        <v>-16.00494665284879</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-17.95997691413991</v>
+        <v>-17.91193191743654</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-20.49634710460685</v>
+        <v>-20.47274629829008</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-22.00352340174464</v>
+        <v>-21.95594973690755</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-26.72168491903898</v>
+        <v>-26.67287385258513</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-31.03875229747266</v>
+        <v>-30.96598295608057</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-30.48304695047501</v>
+        <v>-30.38415512043543</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-31.40725827333451</v>
+        <v>-31.30769733630555</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-27.13305962175604</v>
+        <v>-27.00960857470953</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-28.98074000353405</v>
+        <v>-28.83219301331511</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-29.47462744319368</v>
+        <v>-29.30262868362669</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>143</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.540831838033348</v>
+        <v>-3.546147339138784</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-7.208006744211914</v>
+        <v>-7.209298388721557</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.38960359309633</v>
+        <v>-10.38991283628121</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-13.74585801828528</v>
+        <v>-13.74655321512829</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-15.68068520824112</v>
+        <v>-15.6326927961646</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-16.78248084412137</v>
+        <v>-16.75889651602463</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-16.17736284278902</v>
+        <v>-16.1297893934843</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-15.25356339480692</v>
+        <v>-15.2046941428401</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-16.71526223640753</v>
+        <v>-16.64243455980853</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-20.36294019625443</v>
+        <v>-20.26404566757516</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-19.87730767668324</v>
+        <v>-19.77773684956419</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-23.34485061069162</v>
+        <v>-23.22142604264462</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-25.87115283718791</v>
+        <v>-25.7226234637601</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-26.35505198319284</v>
+        <v>-26.18305322362618</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>143</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.149090458382403</v>
+        <v>-2.15436702116731</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.031851398713442</v>
+        <v>-3.033055361664992</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6448097725356305</v>
+        <v>-0.6449045945816039</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5151547286214893</v>
+        <v>-0.5155865079770621</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.443428604614482</v>
+        <v>-2.39525424899324</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.842374999129547</v>
+        <v>-2.818602710472454</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.625881544587415</v>
+        <v>-3.578180658789776</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.789097599952349</v>
+        <v>-4.740149323489504</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.060274681433867</v>
+        <v>-1.987347392101064</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.513235589010051</v>
+        <v>-1.41423890563528</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.718162428480198</v>
+        <v>-1.618519245389493</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9859915062869078</v>
+        <v>-0.8625060821805235</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.104838947710611</v>
+        <v>-1.956279650565925</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.376031004171544</v>
+        <v>-5.204032244605038</v>
       </c>
     </row>
     <row r="20">
@@ -1303,98 +1303,98 @@
         <v>142</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.002339990680589</v>
+        <v>0.9971839235844442</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.772713827973007</v>
+        <v>-4.773988638473632</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.170359874948986</v>
+        <v>-5.170584206179896</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.342439988083903</v>
+        <v>-4.342967614454565</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.477202629378674</v>
+        <v>-3.429111438916877</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.582507164915704</v>
+        <v>-4.558806740037802</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.178599854843121</v>
+        <v>-8.131040431875284</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-7.24236417049633</v>
+        <v>-7.193509541972425</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-10.11566944966295</v>
+        <v>-10.0429069997957</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-10.26593519622976</v>
+        <v>-10.16709011473373</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-11.17850622651531</v>
+        <v>-11.07898325306881</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-15.37100893164047</v>
+        <v>-15.24763590352019</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-15.79816779547653</v>
+        <v>-15.64966673663463</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-14.8756862784747</v>
+        <v>-14.7036875189082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.5325</t>
+          <t>X ≈ 0.5324</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-7.9650932054397</v>
+        <v>-8.232636514738999</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-14.26768671209777</v>
+        <v>-13.73750144138333</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-12.56911547190311</v>
+        <v>-11.87090348330544</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-11.15976045326285</v>
+        <v>-10.22229841911494</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-14.58557106978532</v>
+        <v>-14.85688334273549</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-15.51346202541018</v>
+        <v>-14.95977676082182</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-18.4331606613739</v>
+        <v>-18.37052630476501</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-16.04046505748298</v>
+        <v>-16.2136386809355</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-15.67231447515793</v>
+        <v>-16.60761360309591</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.99848017039549</v>
+        <v>-14.03321873339466</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-10.10833370504385</v>
+        <v>-12.31733454602153</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-10.42845912169869</v>
+        <v>-13.33708427248781</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-9.573336302667805</v>
+        <v>-13.31589022190479</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-12.16268697115572</v>
+        <v>-16.40335923340572</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>99</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.04012452772006</v>
+        <v>-4.583867324417497</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.607253638749697</v>
+        <v>-4.687368992697415</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.532614260096736</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.20900820089183</v>
+        <v>2.208513708513827</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.359584382507016</v>
+        <v>-1.311038462741244</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.9579916673299707</v>
+        <v>0.9819490762795837</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.157021722239101</v>
+        <v>-2.10901004324878</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.613989355925071</v>
+        <v>-1.564741793531354</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.674971512447613</v>
+        <v>-1.601714402667916</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.555193339080624</v>
+        <v>-5.455846013786051</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.780096517542489</v>
+        <v>-7.680188481523814</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-10.77602139549042</v>
+        <v>-10.65232477446218</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-11.19617224880406</v>
+        <v>-11.04748270102623</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.930032558173259</v>
+        <v>-6.758033798606597</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>137</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-5.78944252521304</v>
+        <v>-5.794783357733614</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.376773656444897</v>
+        <v>-7.377960442889552</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-10.69125307039693</v>
+        <v>-10.69140646040125</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-9.831100919509467</v>
+        <v>-9.83159541188747</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-14.01902550910143</v>
+        <v>-13.97047958933565</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-10.80194345026926</v>
+        <v>-10.77798604131964</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-13.80636183873243</v>
+        <v>-13.75835015974211</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-14.27343048251925</v>
+        <v>-14.22418292012553</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-15.0643396463413</v>
+        <v>-14.9910825365616</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-13.72447742077318</v>
+        <v>-13.6251300954786</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-14.65910558633281</v>
+        <v>-14.55919755031413</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-13.16487341937902</v>
+        <v>-13.04117679835078</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-17.96458631648797</v>
+        <v>-17.81589676871014</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-17.73885066626143</v>
+        <v>-17.56685190669477</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>138</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.055495630047574</v>
+        <v>-1.060836462568147</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.541377485917103</v>
+        <v>-5.542564272361759</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.037598146034384</v>
+        <v>-3.037751536038705</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.805923727083702</v>
+        <v>-5.806418219461705</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.046839250544309</v>
+        <v>-6.022881841594696</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.059085841694618</v>
+        <v>-1.011074162704297</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-4.424705210118873</v>
+        <v>-4.375457647725156</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.485687366641727</v>
+        <v>-4.412430256862031</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.335606162971672</v>
+        <v>-5.236258837677099</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-6.989582683550545</v>
+        <v>-6.889674647531869</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-10.57839293699232</v>
+        <v>-10.45469631596407</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-11.72318147146523</v>
+        <v>-11.5744919236874</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-12.22208350239811</v>
+        <v>-12.05008474283145</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>138</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.229408673525825</v>
+        <v>-3.234749506046398</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.704999325677186</v>
+        <v>1.70381253923253</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.907373002446022</v>
+        <v>-2.907867494824025</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.996387193222873</v>
+        <v>-1.947841273457101</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.32220156938488</v>
+        <v>-5.298244160435267</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.07687912316250589</v>
+        <v>-0.02763156076878914</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.58713664200404</v>
+        <v>-1.513879532224344</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.16169311949325</v>
+        <v>-3.062345794198677</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.917118915434763</v>
+        <v>-1.817210879416088</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.607378444238769</v>
+        <v>-2.483681823210524</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.57825393523342</v>
+        <v>-1.429564387455592</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.09675707731202721</v>
+        <v>0.2687558368786895</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>137</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.509827547779651</v>
+        <v>1.504486715259077</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>7.221766489540585</v>
+        <v>7.220579703095929</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.9875790463913035</v>
+        <v>0.9874256563869821</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.071976831918064</v>
+        <v>-1.072471324296068</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.769295658781779</v>
+        <v>2.817841578547551</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.986377717613955</v>
+        <v>6.010335126563568</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.361521372946328</v>
+        <v>7.409533051936648</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>9.084233751057475</v>
+        <v>9.133481313451192</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>11.21303261643243</v>
+        <v>11.28628972621213</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>12.5528948420003</v>
+        <v>12.65224216729487</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>13.80804769833873</v>
+        <v>13.9079557343574</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>14.57235285799332</v>
+        <v>14.69604947902156</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>16.34198302657781</v>
+        <v>16.49067257435564</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>15.10786466220572</v>
+        <v>15.27986342177238</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>139</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.452063540007686</v>
+        <v>1.446722707487112</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.620128092229244</v>
+        <v>5.618941305784588</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.067083326179073</v>
+        <v>3.066929936174752</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.794430771925789</v>
+        <v>6.793936279547786</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.536716758398441</v>
+        <v>5.585262678164213</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.114666327601867</v>
+        <v>5.13862373655148</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.468804889199014</v>
+        <v>6.516816568189334</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.440585166275582</v>
+        <v>7.489832728669299</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.25730085147951</v>
+        <v>10.33055796125921</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>16.60162665946612</v>
+        <v>16.70097398476069</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>14.95807658034262</v>
+        <v>15.0579846163613</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>16.43130365356125</v>
+        <v>16.5550002745895</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>16.01115280024791</v>
+        <v>16.15984234802574</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>16.95631291090594</v>
+        <v>17.12831167047261</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>137</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6799534741183209</v>
+        <v>-0.6852943066388946</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.267284605350135</v>
+        <v>-2.26847139179479</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7.771545041199772</v>
+        <v>-7.771698431204094</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.451538875713887</v>
+        <v>-5.45203336809189</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.800047406911645</v>
+        <v>-3.751501487145873</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.042819362678017</v>
+        <v>-2.018861953728404</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.587383736542726</v>
+        <v>-3.539372057552406</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.704087416825985</v>
+        <v>-7.654839854432268</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-7.035142566049402</v>
+        <v>-6.961885456269705</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.69528034048146</v>
+        <v>-5.595933015186887</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.629908506040834</v>
+        <v>-6.530000470022159</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-8.785311375583326</v>
+        <v>-8.661614754555082</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-7.745608214298272</v>
+        <v>-7.596918666520445</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.600164534874409</v>
+        <v>-4.428165775307747</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>137</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.969681562378113</v>
+        <v>2.96434072985754</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.302058460343467</v>
+        <v>4.300871673898811</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.097068097486108</v>
+        <v>6.096914707481787</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.847731197278982</v>
+        <v>1.847236704900979</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.229149673380327</v>
+        <v>4.277695593146099</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.256450710314638</v>
+        <v>5.280408119264251</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.711886336449965</v>
+        <v>3.759898015440285</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.05503667076551</v>
+        <v>1.104284233159227</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4657995003558923</v>
+        <v>-0.392542390576196</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.045645303984976</v>
+        <v>-1.946297978690403</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.250346462245219</v>
+        <v>-2.150438426226543</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-4.405749331787696</v>
+        <v>-4.282052710759451</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.825900185101105</v>
+        <v>-4.677210637323277</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.600164534874622</v>
+        <v>-4.42816577530796</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>139</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-11.4975767477621</v>
+        <v>-11.50291758028267</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-8.768361116403938</v>
+        <v>-8.769547902848593</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-8.443708040727316</v>
+        <v>-8.443861430731637</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-9.752331818002268</v>
+        <v>-9.752826310380271</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-8.132347989803002</v>
+        <v>-8.08380207003723</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.115549499736211</v>
+        <v>-7.091592090786598</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-9.358533240297348</v>
+        <v>-9.310521561307027</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-7.667328502789168</v>
+        <v>-7.618080940395451</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.28946173844863</v>
+        <v>-6.216204628668933</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-7.139380534778454</v>
+        <v>-7.04003320948388</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-8.063506153470335</v>
+        <v>-7.96359811745166</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-8.748552461546673</v>
+        <v>-8.624855840518428</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.29100547313346</v>
+        <v>-6.142315925355632</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-10.38181658549694</v>
+        <v>-10.20981782593027</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>137</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.599661503315311</v>
+        <v>-3.605002335835884</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-7.376773656444897</v>
+        <v>-7.377960442889552</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.311691026601437</v>
+        <v>-6.311844416605759</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.80190383921741</v>
+        <v>-1.802398331595413</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.259901421510186</v>
+        <v>-5.211355501744414</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.772746369977284</v>
+        <v>-2.748788961027671</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.587383736542769</v>
+        <v>-3.539372057552448</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.784379387628697</v>
+        <v>-4.73513182523498</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-7.035142566049366</v>
+        <v>-6.96188545626967</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-7.885061362379183</v>
+        <v>-7.78571403708461</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-7.359835513340066</v>
+        <v>-7.259927477321391</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-5.865603346386202</v>
+        <v>-5.741906725357957</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.095973177801838</v>
+        <v>-3.94728363002401</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.410383512976722</v>
+        <v>-2.23838475341006</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>138</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.567692775749535</v>
+        <v>2.562351943228961</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.777463093793131</v>
+        <v>6.776276307348475</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.831967071356992</v>
+        <v>7.831813681352671</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.512916852626454</v>
+        <v>6.512422360248451</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.24998961837133</v>
+        <v>5.298535538137102</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.996639010325275</v>
+        <v>7.020596419274888</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.361204013377936</v>
+        <v>8.409215692368257</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.343410731909991</v>
+        <v>9.392658294303708</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>16.5288053869815</v>
+        <v>16.6020624967612</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.50497354717334</v>
+        <v>13.60432087246791</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.3002723889131</v>
+        <v>13.40018042493178</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.05928822242783</v>
+        <v>14.18298484345608</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.18986200679564</v>
+        <v>12.33855155457346</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.69095997586276</v>
+        <v>11.86295873542942</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>138</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.843055094590106</v>
+        <v>1.837714262069532</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.4296370068366</v>
+        <v>2.428450220391944</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.759503303240962</v>
+        <v>2.75934991323664</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.458097640127178</v>
+        <v>-1.458592132505181</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.996387193222894</v>
+        <v>-1.947841273457122</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.4748998798904793</v>
+        <v>0.4988572888400924</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.013377926421413</v>
+        <v>4.061389605411733</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.343410731910033</v>
+        <v>9.39265829430375</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.557790894227828</v>
+        <v>8.631048004007525</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.432509779057398</v>
+        <v>8.531857104351971</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.503170939637798</v>
+        <v>7.603078975656473</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.16073749779023</v>
+        <v>11.28443411881847</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.91449968795506</v>
+        <v>13.06318923573289</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.69095997586276</v>
+        <v>11.86295873542942</v>
       </c>
     </row>
     <row r="34">
@@ -2028,49 +2028,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.915518862706051</v>
+        <v>7.34390277365317</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>8.22673845611196</v>
+        <v>8.680433717694392</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.55660475251635</v>
+        <v>9.016622736678954</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.13610525842355</v>
+        <v>9.876433785192901</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>13.22100411112498</v>
+        <v>13.03681968073736</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.06910277844118</v>
+        <v>11.8497511849577</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.15830546265329</v>
+        <v>13.97887611763008</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>14.41587450002597</v>
+        <v>14.97289737184527</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.90561698118437</v>
+        <v>13.47607074810994</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.78033586601391</v>
+        <v>12.65224216729496</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.1988231135508</v>
+        <v>16.09773675625519</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.23320126590615</v>
+        <v>16.15590349362011</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>16.53768809375217</v>
+        <v>16.49067257435555</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>16.7634237439787</v>
+        <v>16.73971743637092</v>
       </c>
     </row>
   </sheetData>
@@ -2210,157 +2210,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.01924</t>
+          <t>X &gt; 0.01927</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.05121732311557281</v>
+        <v>0.03966962241754146</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0867454155387648</v>
+        <v>-0.09766102566100443</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04308265336134554</v>
+        <v>0.03192353896024258</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08914944278690484</v>
+        <v>0.07785106752299242</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.07582231605757528</v>
+        <v>0.06367120073846877</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.00336452190813219</v>
+        <v>-0.01489021377621214</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1202611011187997</v>
+        <v>0.1079553303313787</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.08108871076990454</v>
+        <v>0.06896329432137804</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2286993424427592</v>
+        <v>0.2400610157498377</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1973799665545215</v>
+        <v>0.2084877595768049</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2748304978528182</v>
+        <v>0.2614479411250414</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2497846266543817</v>
+        <v>0.2603077597919778</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2096338591507134</v>
+        <v>0.2198422779404723</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2050545769138736</v>
+        <v>0.1903784604024921</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.05235</t>
+          <t>X &gt; 0.05237</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3952</v>
+        <v>3963</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2568935725768426</v>
+        <v>0.2564877726985344</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1460411660082741</v>
+        <v>0.1457048006489785</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4210245486742821</v>
+        <v>0.4198679179484444</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.6660674353361031</v>
+        <v>0.6642515551400479</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5960996989028828</v>
+        <v>0.5916744671620151</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.6549613642997869</v>
+        <v>0.6517775549724547</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.7357606097955554</v>
+        <v>0.7309767262090077</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.6869380586963629</v>
+        <v>0.6822175962854047</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.8422400267502823</v>
+        <v>0.8357143200430599</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.7648319900449252</v>
+        <v>0.7570263447884713</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.751489890149891</v>
+        <v>0.7436871889476961</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8255788252296767</v>
+        <v>0.8162066940692867</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.6981312721123913</v>
+        <v>0.6876792107252143</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4576090399946509</v>
+        <v>0.4464868048542101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.08546</t>
+          <t>X &gt; 0.08548</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3810</v>
+        <v>3821</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.09789706936521725</v>
+        <v>0.09813021997477733</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.01046947053695391</v>
+        <v>-0.01032517406579814</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2631919195452355</v>
+        <v>0.262451180974395</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3553935200518978</v>
+        <v>0.3544207032852285</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.09327889282286606</v>
+        <v>0.08833385046919062</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.2740966670390677</v>
+        <v>0.2710004677076938</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2823576623852375</v>
+        <v>0.2769182047484193</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2751854106084153</v>
+        <v>0.26964598284777</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.4908545065894216</v>
+        <v>0.4823779584761922</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3110199209450286</v>
+        <v>0.3005413896603031</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4095894848891604</v>
+        <v>0.3987705650082205</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4850679873198445</v>
+        <v>0.4717329622034541</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3946772061232906</v>
+        <v>0.3791858684997109</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2416846135439101</v>
+        <v>0.2243786535781638</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3667</v>
+        <v>3678</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1949883836707542</v>
+        <v>-0.1936664171384024</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3003108759765496</v>
+        <v>-0.2992509696634329</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1638718770318519</v>
+        <v>-0.1633619485066404</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.07326517194462667</v>
+        <v>-0.0729779981406935</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4063633803197533</v>
+        <v>-0.4118924049296027</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2030060650962113</v>
+        <v>-0.205728020241672</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.30012944618516</v>
+        <v>-0.3059043595460977</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2895552517466555</v>
+        <v>-0.2955350682983351</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2266649170821893</v>
+        <v>-0.2361719293328832</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4623141247085059</v>
+        <v>-0.4747476866800042</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3793864192849341</v>
+        <v>-0.3921491641448682</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3297764439306761</v>
+        <v>-0.3460006637902495</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4893218472969423</v>
+        <v>-0.5085516673953308</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.7664055600766702</v>
+        <v>-0.7880567030177588</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3525</v>
+        <v>3536</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5545166113601852</v>
+        <v>-0.551813712742721</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6852601671378977</v>
+        <v>-0.6829168694565979</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6972807481722256</v>
+        <v>-0.6950900503169422</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7215705712712221</v>
+        <v>-0.7192409958907504</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9617177707185078</v>
+        <v>-0.967689600351477</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.8472100812625385</v>
+        <v>-0.8490015131358959</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.9167023335618438</v>
+        <v>-0.9227186791420081</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9720560037111099</v>
+        <v>-0.9781303373544432</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9893618749966109</v>
+        <v>-0.999818573435185</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.342193404913097</v>
+        <v>-1.356376744825141</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.446350898082805</v>
+        <v>-1.460318119240561</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.481488313035591</v>
+        <v>-1.499747560833519</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.772668922861477</v>
+        <v>-1.794649020711411</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.013634535392249</v>
+        <v>-2.039182388578723</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3382</v>
+        <v>3393</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8700139967846638</v>
+        <v>-0.8659544555387768</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9394798489959442</v>
+        <v>-0.9361670304539942</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9354440948548444</v>
+        <v>-0.9323853002376836</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.113723836462974</v>
+        <v>-1.110007976155494</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.400393535672407</v>
+        <v>-1.407238558941337</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.205233504744641</v>
+        <v>-1.206949613648092</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.185667578857817</v>
+        <v>-1.193086097913074</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.282754933781327</v>
+        <v>-1.290151227678415</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.209734554739441</v>
+        <v>-1.223000839728336</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.512104446611808</v>
+        <v>-1.530516772000993</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.700690940352793</v>
+        <v>-1.7186294280922</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.797942736560699</v>
+        <v>-1.821155943293348</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.113324856763413</v>
+        <v>-2.141391738364625</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.492397783459836</v>
+        <v>-2.524719220464434</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3240</v>
+        <v>3251</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.013839544472162</v>
+        <v>-1.008886334690906</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.478325985836797</v>
+        <v>-1.473000831587427</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.395517002662665</v>
+        <v>-1.390766935144789</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.648956057072546</v>
+        <v>-1.64325141280063</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.832457154548763</v>
+        <v>-1.840257028769621</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.703475218274733</v>
+        <v>-1.704628265099721</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.617907139391846</v>
+        <v>-1.626282212454655</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.729749545622184</v>
+        <v>-1.738105767939004</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.466103167986049</v>
+        <v>-1.48227678323029</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.744584164722873</v>
+        <v>-1.767348131739652</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.870865446424503</v>
+        <v>-1.893371324086111</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.973935141214163</v>
+        <v>-2.002966140473973</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.284781263978722</v>
+        <v>-2.319986335153253</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.597821559295589</v>
+        <v>-2.63871076202733</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3098</v>
+        <v>3109</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.106506768644131</v>
+        <v>-1.100758846027283</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.616217879225189</v>
+        <v>-1.610110441603233</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.801122463001015</v>
+        <v>-1.794719206049848</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.911345919462413</v>
+        <v>-1.904433655475657</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.175272645894019</v>
+        <v>-2.184429201430248</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.957512375025203</v>
+        <v>-1.958912863619773</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.864238820760555</v>
+        <v>-1.874313916383208</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.95990990158765</v>
+        <v>-1.970079277520284</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.842616378771183</v>
+        <v>-1.861538072896217</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.127297357993029</v>
+        <v>-2.154279107978745</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.250111077850725</v>
+        <v>-2.276862159174584</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.262824914552006</v>
+        <v>-2.297805619557295</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.536487306447057</v>
+        <v>-2.579198573577891</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.712909748410034</v>
+        <v>-2.763115168757125</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2954</v>
+        <v>2965</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.106051747337766</v>
+        <v>-1.099769313134132</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.496013114832166</v>
+        <v>-1.489997005440891</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.67068463820145</v>
+        <v>-1.664446253196253</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.893760375561079</v>
+        <v>-1.886554621848745</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.414343925285458</v>
+        <v>-2.4254101554586</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.031729992209264</v>
+        <v>-2.034084111297375</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.233777118143443</v>
+        <v>-2.245298907666857</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.142586134521615</v>
+        <v>-2.154959011146516</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.050473746685903</v>
+        <v>-2.073094874048387</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.307708347173609</v>
+        <v>-2.340148792329188</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.528049500193021</v>
+        <v>-2.559915672571989</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.543151423784181</v>
+        <v>-2.584794057790916</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.742088261724916</v>
+        <v>-2.793329571620006</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.938184490495814</v>
+        <v>-2.998345856793861</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2813</v>
+        <v>2824</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.230885642047937</v>
+        <v>-1.223541504125613</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.596526902359251</v>
+        <v>-1.589762816953979</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.760244613169085</v>
+        <v>-1.753340831338136</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.284384815349334</v>
+        <v>-2.275279766105456</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.556171085826527</v>
+        <v>-2.569653558278333</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.275692211515079</v>
+        <v>-2.278408739162856</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.483692687207949</v>
+        <v>-2.497208523994075</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.435614618841342</v>
+        <v>-2.449918650439429</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.584349178390212</v>
+        <v>-2.609673098855666</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.81210752890204</v>
+        <v>-2.849156773433329</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.068922275118474</v>
+        <v>-3.105256280132693</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.15774269373037</v>
+        <v>-3.205242486615553</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.381350254877361</v>
+        <v>-3.440081252916592</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.598817815653859</v>
+        <v>-3.667997457862036</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2670</v>
+        <v>2681</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.218896970748816</v>
+        <v>-1.210928454434125</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.593966403985952</v>
+        <v>-1.586790581041718</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.969156238677733</v>
+        <v>-1.961023926589334</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.379036424466349</v>
+        <v>-2.369034347295219</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.785942023870255</v>
+        <v>-2.801782332667273</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.693157614887156</v>
+        <v>-2.695584909919219</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.982610444727349</v>
+        <v>-2.997357806596547</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.019298048229047</v>
+        <v>-3.034594770641263</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.098175515090865</v>
+        <v>-3.126643515087721</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.180662692298554</v>
+        <v>-3.22346635123867</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.365580991916076</v>
+        <v>-3.407957979785344</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.685656670395161</v>
+        <v>-3.740116595015827</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.973817665910133</v>
+        <v>-4.041178043714631</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.215244225407403</v>
+        <v>-4.294758750475147</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2527</v>
+        <v>2538</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.599259181342795</v>
+        <v>-1.588904455228025</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.024358917611579</v>
+        <v>-2.014857537493818</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.477417243577811</v>
+        <v>-2.466626741433259</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.99677449799308</v>
+        <v>-2.983516483516496</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.23878649830219</v>
+        <v>-3.256285991027646</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.999930752130787</v>
+        <v>-3.002514570399185</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.379985376141988</v>
+        <v>-3.396541546890312</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.313575027085712</v>
+        <v>-3.331227404356348</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.314590450644751</v>
+        <v>-3.347842613601479</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.47233392710217</v>
+        <v>-3.521872128592534</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.577197966818083</v>
+        <v>-3.626666246183625</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.877858269569288</v>
+        <v>-3.941515898298974</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.15862909575435</v>
+        <v>-4.237357025205171</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.268274494753143</v>
+        <v>-4.361730338473343</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2386</v>
+        <v>2397</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.316775994450616</v>
+        <v>-1.306792322812299</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.423211381312946</v>
+        <v>-1.415829383268239</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.962885189621467</v>
+        <v>-1.953804306995416</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.228100785466026</v>
+        <v>-2.217550002967542</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.36884188445763</v>
+        <v>-2.394189171827115</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.965984940857048</v>
+        <v>-1.974853880523256</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.279432626095897</v>
+        <v>-2.304811653359884</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.930279346127868</v>
+        <v>-1.958189377989939</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.676238891381239</v>
+        <v>-1.723246122867415</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.876143425720969</v>
+        <v>-1.941737834954715</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.932588367816059</v>
+        <v>-1.998370299705861</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.503598675831519</v>
+        <v>-2.584569270274827</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.691773421824365</v>
+        <v>-2.790601967081052</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.778712145327283</v>
+        <v>-2.894618671111374</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2243</v>
+        <v>2254</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.174983758323854</v>
+        <v>-1.164721441119887</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.054408110294411</v>
+        <v>-1.048275670854835</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.425649018557301</v>
+        <v>-1.418594227275861</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.493798830810135</v>
+        <v>-1.486118122160534</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.520159942727339</v>
+        <v>-1.554301852270662</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.021375527496907</v>
+        <v>-1.03691328741025</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.39338535860275</v>
+        <v>-1.427716792296096</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.080868013554934</v>
+        <v>-1.117794443928908</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.7174424855235699</v>
+        <v>-0.7767315059718669</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6975380141354606</v>
+        <v>-0.7793199023616779</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7885425090697353</v>
+        <v>-0.8703980651762464</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.174887562730753</v>
+        <v>-1.275309945319691</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.213997560746797</v>
+        <v>-1.335731038054831</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.275628508762516</v>
+        <v>-1.417135911124859</v>
       </c>
     </row>
     <row r="20">
@@ -2942,205 +2942,205 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2100</v>
+        <v>2111</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.108651730653207</v>
+        <v>-1.097682446355904</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9197536387496967</v>
+        <v>-0.9138258860202271</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.478820452929256</v>
+        <v>-1.471004278187884</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.560439833959173</v>
+        <v>-1.551862329090063</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.457289743370268</v>
+        <v>-1.497335394321198</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.897374134904787</v>
+        <v>-0.9162209200498097</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.241362999271423</v>
+        <v>-1.282043493902627</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.8283552369573854</v>
+        <v>-0.8724146486768092</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.626002007421107</v>
+        <v>-0.6947238926528314</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.641992893560662</v>
+        <v>-0.7363102304203579</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7252398193194054</v>
+        <v>-0.8197200316516131</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.187750484669557</v>
+        <v>-1.303273447180842</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.153335504396402</v>
+        <v>-1.293694822238123</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.9964106245513236</v>
+        <v>-1.160610010751732</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.5159</t>
+          <t>X &gt; 0.5158</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1958</v>
+        <v>1969</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.261747146602843</v>
+        <v>-1.248759655361255</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6403254738519877</v>
+        <v>-0.6354393391190598</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.211099003528439</v>
+        <v>-1.204198615529251</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.35868088509006</v>
+        <v>-1.350573882913451</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.310799636213375</v>
+        <v>-1.358019905071529</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.630117296160364</v>
+        <v>-0.653525548572766</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7382538912575356</v>
+        <v>-0.7881087223474665</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.363192178447413</v>
+        <v>-0.4165510250871876</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.06221697970777029</v>
+        <v>-0.02055324703867711</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.05596410693933507</v>
+        <v>-0.05618288477662503</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.03286223881226391</v>
+        <v>-0.07984426860376459</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1591382786073083</v>
+        <v>-0.2976363375819631</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.09124858645290601</v>
+        <v>-0.2583733332364417</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.01015584268929359</v>
+        <v>-0.1839126993458322</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.549</t>
+          <t>X &gt; 0.5489</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1836</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8163178333250158</v>
+        <v>-0.7428470070512034</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2651963513473561</v>
+        <v>0.313675181360864</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4563724190285967</v>
+        <v>-0.4315015853471991</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7074108919979736</v>
+        <v>-0.7079053843759766</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4287069810413797</v>
+        <v>-0.3801610612756079</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3588631270250744</v>
+        <v>0.3828205359746875</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4375514605693667</v>
+        <v>0.4855631395596873</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6785438189612734</v>
+        <v>0.7277913813549901</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.107757740869872</v>
+        <v>1.181014850649568</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.856967484845029</v>
+        <v>0.9563148101396024</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7067325575216614</v>
+        <v>0.8066405935403367</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5232457861296993</v>
+        <v>0.6469424071579439</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.5388247803108399</v>
+        <v>0.6875143280886675</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8190266614741972</v>
+        <v>0.9910254210408596</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.5821</t>
+          <t>X &gt; 0.582</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1737</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5185879181004296</v>
+        <v>-0.5239287506210033</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5998955735808593</v>
+        <v>0.5987087871362036</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5432926217671437</v>
+        <v>-0.543446011771465</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.8736316693129353</v>
+        <v>-0.8741261616909384</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3756517923568126</v>
+        <v>-0.3271058725910407</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3247159045206445</v>
+        <v>0.3486733134702575</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5854286886050843</v>
+        <v>0.633440367595405</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.8092063315195546</v>
+        <v>0.8584538939132713</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.266358890022687</v>
+        <v>1.339615999802383</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.222427428177575</v>
+        <v>1.321774753472148</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.190437841592683</v>
+        <v>1.290345877611358</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.167245470056237</v>
+        <v>1.290942091084482</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.207658807876967</v>
+        <v>1.356348355654795</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.260682886428199</v>
+        <v>1.432681645994862</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1600</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.0672709923664101</v>
+        <v>-0.07261182488698381</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.282897876401819</v>
+        <v>1.281711089957163</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3256264916467799</v>
+        <v>0.3254731016424586</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1066483647648582</v>
+        <v>-0.1071428571428612</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.7925620821394475</v>
+        <v>0.8411080019052193</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.277436111774534</v>
+        <v>1.301393520724147</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.817725752508359</v>
+        <v>1.86573743149868</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.100657108721627</v>
+        <v>2.149904671115344</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.664674952198851</v>
+        <v>2.737932061978547</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.502256155868984</v>
+        <v>2.601603481163558</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.547554997608799</v>
+        <v>2.647463033627474</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.394433149964129</v>
+        <v>2.518129770992374</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.849282296650713</v>
+        <v>2.997971844428541</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.887517946877246</v>
+        <v>3.059516706443908</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1462</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.02600876139555908</v>
+        <v>0.02066792887498536</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.927049723187054</v>
+        <v>1.925862936742398</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6430854519750966</v>
+        <v>0.6429320619707752</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.431313331541574</v>
+        <v>0.430818839163571</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.32941228733781</v>
+        <v>1.377958207103582</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.968783580994781</v>
+        <v>1.992740989944394</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.089271580141741</v>
+        <v>2.137283259132062</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.716594181225041</v>
+        <v>2.765841743618758</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.339606552746048</v>
+        <v>3.412863662525744</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.242081737264343</v>
+        <v>3.341429062558916</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.447777295830406</v>
+        <v>3.547685331849081</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.618954353794493</v>
+        <v>3.742650974822737</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.224795292546744</v>
+        <v>4.373484840324572</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.313732037164527</v>
+        <v>4.48573079673119</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1324</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.3653196420746809</v>
+        <v>0.3599788095541072</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.95019394890938</v>
+        <v>1.949007162464724</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.177779059622608</v>
+        <v>1.177625669618287</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7793032968665656</v>
+        <v>0.7788088044885626</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.676059060991406</v>
+        <v>1.724604980757178</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.728720099689937</v>
+        <v>2.75267750863955</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.795067142236462</v>
+        <v>2.843078821226783</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.007756806606821</v>
+        <v>3.057004369000538</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.853119060960182</v>
+        <v>3.926376170739879</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.909544675506446</v>
+        <v>4.008892000801019</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.00695832087164</v>
+        <v>4.106866356890315</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.267922575945995</v>
+        <v>4.39161919697424</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.82964483441507</v>
+        <v>4.978334382192898</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.753265681016217</v>
+        <v>4.925264440582879</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1187</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2332239528736864</v>
+        <v>0.2278831203531126</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.341764767724477</v>
+        <v>1.340577981279822</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.199731377914681</v>
+        <v>1.199577987910359</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.9929725282427171</v>
+        <v>0.9924780358647141</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.549880953243068</v>
+        <v>1.59842687300884</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.352730972768633</v>
+        <v>2.376688381718246</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.268020613502465</v>
+        <v>2.316032292492785</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.306427959606204</v>
+        <v>2.35567552199992</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.003659787919155</v>
+        <v>3.076916897698851</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.911954976425015</v>
+        <v>3.011302301719589</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.875745814794982</v>
+        <v>2.975653850813657</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.078615963780464</v>
+        <v>3.202312584808709</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.500925093617852</v>
+        <v>3.649614641395679</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.558168747214225</v>
+        <v>3.730167506780887</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1048</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0715648854961799</v>
+        <v>0.06622405297560618</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7743100901422721</v>
+        <v>0.7731233036976164</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.9520577893567079</v>
+        <v>0.9519043993523866</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2235043069908613</v>
+        <v>0.2230098146128583</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.021092616490591</v>
+        <v>1.069638536256363</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.98640557742339</v>
+        <v>2.010362986373003</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.710855523500733</v>
+        <v>1.758867202491054</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.625466269026965</v>
+        <v>1.674713831420682</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.041583349145412</v>
+        <v>2.114840458925109</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.096244705487315</v>
+        <v>1.195592030781889</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.273222936540094</v>
+        <v>1.373130972558769</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.307601088895417</v>
+        <v>1.431297709923662</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.841648708864447</v>
+        <v>1.990338256642275</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.78112481710626</v>
+        <v>1.953123576672922</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>911</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1845813676774952</v>
+        <v>0.1792405351569215</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.231717854447929</v>
+        <v>1.230531068003273</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.263949762777401</v>
+        <v>2.263796372773079</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.076941097364674</v>
+        <v>1.076446604986671</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.746115869186646</v>
+        <v>1.794661788952418</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.592337319238858</v>
+        <v>2.616294728188471</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.50762695997269</v>
+        <v>2.555638638963011</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.02848367293678</v>
+        <v>3.077731235330496</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.4065794527477</v>
+        <v>3.479836562527396</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.117582720084144</v>
+        <v>2.216930045378717</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.46172898224107</v>
+        <v>2.561637018259745</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.825415586846667</v>
+        <v>2.949112207874911</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.283420606200657</v>
+        <v>3.432110153978485</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.740769867843213</v>
+        <v>2.912768627409875</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>774</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3083885634258436</v>
+        <v>-0.3137293959464174</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.6882596335077622</v>
+        <v>0.6870728470631065</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.585477912835408</v>
+        <v>1.585324522831087</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.9405092579741563</v>
+        <v>0.9400147655961533</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.306612469736343</v>
+        <v>1.355158389502115</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.120782365004516</v>
+        <v>2.144739773954129</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.294469938554876</v>
+        <v>2.342481617545197</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.377788891667365</v>
+        <v>3.427036454061081</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.092000533594202</v>
+        <v>4.165257643373899</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.854484838039539</v>
+        <v>2.953832163334113</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.295778511820686</v>
+        <v>3.395686547839361</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.105350462625623</v>
+        <v>4.229047083653867</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.718791340578363</v>
+        <v>4.867480888356191</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.040134225947007</v>
+        <v>4.212132985513669</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>635</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.140898298972175</v>
+        <v>2.135557466451601</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.758291577189226</v>
+        <v>2.75710479074457</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.780843027079847</v>
+        <v>3.780689637075525</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.281146910825697</v>
+        <v>3.280652418447694</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.372778617572514</v>
+        <v>3.421324537338286</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.14259359208949</v>
+        <v>4.166551001039103</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.84528480762647</v>
+        <v>4.893296486616791</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.795538998485405</v>
+        <v>5.844786560879122</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.364478101805148</v>
+        <v>6.437735211584844</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.042118360593406</v>
+        <v>5.141465685887979</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.782299092096984</v>
+        <v>5.88220712811566</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.919039449176722</v>
+        <v>7.042736070204967</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.128809855705832</v>
+        <v>7.27749940348366</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.197065190971742</v>
+        <v>7.369063950538404</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>498</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.720128606027167</v>
+        <v>3.714787773506593</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.546452093269288</v>
+        <v>5.545265306824632</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.557303198474095</v>
+        <v>6.557149808469774</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.679496213548397</v>
+        <v>4.679001721170394</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.747632363263946</v>
+        <v>5.796178283029718</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.045006392899033</v>
+        <v>6.068963801848646</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.165115310741299</v>
+        <v>7.21312698973162</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.706078795468606</v>
+        <v>8.755326357862323</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10.05071912890568</v>
+        <v>10.12397623868538</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.598390694021603</v>
+        <v>8.697738019316176</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.397705600018426</v>
+        <v>9.497613636037102</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.21675217616878</v>
+        <v>10.36544172394661</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.840078187841108</v>
+        <v>10.01207694740777</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>360</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.161895674300254</v>
+        <v>4.15655484177968</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.074564543068483</v>
+        <v>5.073377756623827</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.06868204720233</v>
+        <v>6.068528657198009</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.938395415472776</v>
+        <v>5.986941335238548</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.680213889552306</v>
+        <v>5.704171298501919</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.706614641397259</v>
+        <v>6.75462632038758</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.461768219832734</v>
+        <v>8.511015782226451</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.56745272997663</v>
+        <v>7.640709839756326</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.71753393364677</v>
+        <v>6.816881258941343</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.90172166427547</v>
+        <v>8.001629700294146</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.047210927741908</v>
+        <v>9.170907548770153</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.460393407761828</v>
+        <v>9.609082955539655</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.130573502432803</v>
+        <v>9.302572261999465</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>222</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.603337115741695</v>
+        <v>5.597996283221121</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.718708687212633</v>
+        <v>6.717521900767977</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.125739104259395</v>
+        <v>8.125585714255074</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.355063346946856</v>
+        <v>7.354568854568853</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.87082784790523</v>
+        <v>10.919373767671</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.915949625288043</v>
+        <v>8.939907034237656</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.380788815571428</v>
+        <v>8.428800494561749</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.913720171784689</v>
+        <v>7.962967734178406</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.951837114361012</v>
+        <v>7.025094224140709</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.651467867580706</v>
+        <v>5.75081519287528</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.149469412023208</v>
+        <v>8.249377448041884</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.733397113928085</v>
+        <v>7.857093734956329</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.313246260614676</v>
+        <v>7.461935808392504</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.538981910841208</v>
+        <v>7.710980670407871</v>
       </c>
     </row>
     <row r="35">
@@ -3722,49 +3722,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.447609960014546</v>
+        <v>2.784005822171842</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>3.553769913486569</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.417888396408685</v>
+        <v>6.689443689877756</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>3.289915966386545</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.506549178375806</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-0.5166155096777842</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-2.768390510325986</v>
+        <v>-3.335389446531707</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2.829372666848762</v>
+        <v>-3.372362055668503</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.37266122471879</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.074468811915011</v>
+        <v>-4.400331084019577</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-5.518634934889988</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-7.841193893825476</v>
+        <v>-7.090263449689104</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-7.615458243598944</v>
+        <v>-6.841218587673737</v>
       </c>
     </row>
   </sheetData>
@@ -3904,157 +3904,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.01924</t>
+          <t>X &lt; 0.01927</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.50477099236641</v>
+        <v>-1.921876530769339</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.730240501721873</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.105921127400833</v>
+        <v>-1.545850427769302</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-3.768907563025216</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.704461727384363</v>
+        <v>-3.081686115741832</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.7205111677829734</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.872750437967824</v>
+        <v>-5.222497862618958</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.958866700802183</v>
+        <v>-3.335389446531707</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.16270600018211</v>
+        <v>-11.60765617331557</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.631672415559578</v>
+        <v>-10.07854357765996</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.40780214524835</v>
+        <v>-12.63562520166664</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.18294780241683</v>
+        <v>-12.57745846430175</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-10.22214627477786</v>
+        <v>-10.61967521439499</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.996410624551324</v>
+        <v>-9.194159764144331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.05235</t>
+          <t>X &lt; 0.05237</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>227</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.487149846991962</v>
+        <v>-4.492490679512535</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.550251903333866</v>
+        <v>-2.551438689778522</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.350309631701236</v>
+        <v>-7.350463021705558</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-11.62537083172521</v>
+        <v>-11.62586532410322</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.40154584737597</v>
+        <v>-10.3529999276102</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.42575772082458</v>
+        <v>-11.40180031187497</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-12.83205398317445</v>
+        <v>-12.78404230418413</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-11.97753672387749</v>
+        <v>-11.92828916148378</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.68169068656767</v>
+        <v>-14.60843357678797</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-13.32896631109136</v>
+        <v>-13.22961898579679</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-13.09313883499032</v>
+        <v>-12.99323079897164</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-14.3803465857187</v>
+        <v>-14.25664996469045</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.1573256328647</v>
+        <v>-12.00863608508688</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.96683227338707</v>
+        <v>-7.794833513820407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.08546</t>
+          <t>X &lt; 0.08548</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>369</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.014256087217355</v>
+        <v>-1.019596919737928</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1084398818218659</v>
+        <v>0.1072530953772102</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.725355893177067</v>
+        <v>-2.725509283181388</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.67914158969711</v>
+        <v>-3.679636082075113</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.9653986224675961</v>
+        <v>-0.9168527027018243</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.836046273049313</v>
+        <v>-2.812088864099699</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.920756632315481</v>
+        <v>-2.87274495332516</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.845819856048024</v>
+        <v>-2.796572293654307</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.074823692787604</v>
+        <v>-5.001566583007907</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.214715388846457</v>
+        <v>-3.115368063551884</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.232424677187943</v>
+        <v>-4.132516641169268</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.011054654913927</v>
+        <v>-4.887358033885683</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.07619195809184</v>
+        <v>-3.927502410314013</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.495442757729798</v>
+        <v>-2.323443998163135</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>512</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.40147900763359</v>
+        <v>1.396138175113016</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.157897876401819</v>
+        <v>2.156711089957163</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.17718899164678</v>
+        <v>1.177035601642459</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5261641352351418</v>
+        <v>0.5256696428571388</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.917562082139447</v>
+        <v>2.966108001905219</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.457123611774534</v>
+        <v>1.481081020724147</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.153663252508366</v>
+        <v>2.201674931498687</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.077219608721627</v>
+        <v>2.126467171115344</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.625612452198851</v>
+        <v>1.698869561978547</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.314756155868992</v>
+        <v>3.414103481163565</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.719429997608799</v>
+        <v>2.819338033627474</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.363183149964122</v>
+        <v>2.486879770992367</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.505532296650713</v>
+        <v>3.654221844428541</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.489080446877246</v>
+        <v>5.661079206443908</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>654</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.99981616359689</v>
+        <v>2.994475331076316</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.706063014016493</v>
+        <v>3.704876227571837</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.770007225591726</v>
+        <v>3.769853835587405</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.900232369180088</v>
+        <v>3.899737876802085</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.196805201405496</v>
+        <v>5.245351121171268</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.576748038380039</v>
+        <v>4.600705447329652</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.950753275444143</v>
+        <v>4.998764954434463</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.248210625541198</v>
+        <v>5.297458187934915</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.340133667795186</v>
+        <v>5.413390777574882</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.242508449446973</v>
+        <v>7.341855774741546</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.802333285070574</v>
+        <v>7.902241321089249</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.989616636202662</v>
+        <v>8.113313257230907</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>9.557233366987106</v>
+        <v>9.705922914764933</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>10.85330540865095</v>
+        <v>11.02530416821761</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>797</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.706019471874491</v>
+        <v>3.700678639353917</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.000746057079354</v>
+        <v>3.999559270634698</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.982386215611655</v>
+        <v>3.982232825607333</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.739963931345557</v>
+        <v>4.739469438967554</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.958261580257386</v>
+        <v>6.006807500023157</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.126400980030496</v>
+        <v>5.150358388980109</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.041690620764328</v>
+        <v>5.089702299754649</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.452915577981358</v>
+        <v>5.502163140375075</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.14099239260036</v>
+        <v>5.214249502380056</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>6.424072341565356</v>
+        <v>6.52341966685993</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.223135298738036</v>
+        <v>7.323043334756711</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7.633924994380685</v>
+        <v>7.757621615408929</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.970361343074799</v>
+        <v>9.119050890852627</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>10.57627265202154</v>
+        <v>10.7482714115882</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>939</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.51226841125446</v>
+        <v>3.506927578733887</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.119825458936425</v>
+        <v>5.11863867249177</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.831550346811852</v>
+        <v>4.831396956807531</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.707249398813417</v>
+        <v>5.706754906435414</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.34041884465276</v>
+        <v>6.388964764418532</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.892318965874644</v>
+        <v>5.916276374824257</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.594616061347558</v>
+        <v>5.642627740337879</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.979517598604481</v>
+        <v>6.028765160998198</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.066565261038043</v>
+        <v>5.13982237081774</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.027083099425965</v>
+        <v>6.126430424720539</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.461359576948517</v>
+        <v>6.561267612967193</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.815226547195223</v>
+        <v>6.938923168223468</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>7.886023510708213</v>
+        <v>8.034713058486041</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>8.963729341978414</v>
+        <v>9.135728101545077</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>1081</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.184405695885211</v>
+        <v>3.179064863364637</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.64980351932504</v>
+        <v>4.648616732880384</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.180101514773511</v>
+        <v>5.17994812476919</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.49534053440258</v>
+        <v>5.494846042024577</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.252148113591808</v>
+        <v>6.30069403335758</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.624452763023378</v>
+        <v>5.648410171972991</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.354728527716503</v>
+        <v>5.402740206706824</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.627715388092582</v>
+        <v>5.676962950486299</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.289212417508743</v>
+        <v>5.36246952728844</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.104418505545219</v>
+        <v>6.203765830839792</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.454758975407131</v>
+        <v>6.554667011425806</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.489137127762454</v>
+        <v>6.612833748790699</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.271576468713626</v>
+        <v>7.420266016491453</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>7.7748329330012</v>
+        <v>7.946831692567862</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>1225</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.678902477021339</v>
+        <v>2.673561644500765</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.622183590687534</v>
+        <v>3.620996804242878</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.043738736544739</v>
+        <v>4.043585346540418</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.582127145439223</v>
+        <v>4.58163265306122</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.839755959690464</v>
+        <v>5.888301879456236</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.912640193407192</v>
+        <v>4.936597602356805</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.399358405569586</v>
+        <v>5.447370084559907</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.177187720966529</v>
+        <v>5.226435283360246</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.952940258321298</v>
+        <v>5.026197368100995</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.57240921709348</v>
+        <v>5.671756542388053</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>6.102401936384311</v>
+        <v>6.202309972402986</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.136780088739634</v>
+        <v>6.260476709767879</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.614588419099697</v>
+        <v>6.763277966877524</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.085222028509897</v>
+        <v>7.257220788076559</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>1366</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.546473517150432</v>
+        <v>2.541132684629858</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.301748535259797</v>
+        <v>3.300561748815142</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.639041572173873</v>
+        <v>3.638888182169552</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.720950463932063</v>
+        <v>4.72045597155406</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.28075754334003</v>
+        <v>5.329303463105802</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.699654266972196</v>
+        <v>4.723611675921809</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.127389002874395</v>
+        <v>5.175400681864716</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>5.02635256992221</v>
+        <v>5.075600132315927</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.331402624233988</v>
+        <v>5.404659734013684</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.799199786908524</v>
+        <v>5.898547112203097</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>6.326563050317432</v>
+        <v>6.426471086336107</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.507354087006583</v>
+        <v>6.631050708034827</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6.965680539696102</v>
+        <v>7.11437008747393</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.411035516423368</v>
+        <v>7.58303427599003</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>1509</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.167197198488459</v>
+        <v>2.161856365967886</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.833013847243443</v>
+        <v>2.831827060798787</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.498547300129218</v>
+        <v>3.498393910124896</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.225193914890546</v>
+        <v>4.224699422512543</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.946016356493324</v>
+        <v>4.994562276259096</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.779507019660556</v>
+        <v>4.80346442861017</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.291218131567348</v>
+        <v>5.339229810557669</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.354301906601016</v>
+        <v>5.403549468994733</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.492126907135891</v>
+        <v>5.565384016915587</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.636243896094307</v>
+        <v>5.73559122138888</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5.961695156654521</v>
+        <v>6.061603192673196</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.526225727830258</v>
+        <v>6.649922348858503</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.033841607452572</v>
+        <v>7.1825311552304</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7.458384414736763</v>
+        <v>7.630383174303425</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1652</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.458909395042788</v>
+        <v>2.453568562522214</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.111287706910296</v>
+        <v>3.110100920465641</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.806104699879228</v>
+        <v>3.805951309874906</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.602189407632238</v>
+        <v>4.601694915254235</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.971890169306512</v>
+        <v>5.020436089072284</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.60340463477695</v>
+        <v>4.627362043726563</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5.184553839675431</v>
+        <v>5.232565518665751</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.080681321796689</v>
+        <v>5.129928884190406</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.080231852925237</v>
+        <v>5.153488962704934</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.319901434319348</v>
+        <v>5.419248759613922</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.478396401967153</v>
+        <v>5.578304437985828</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.936503367881798</v>
+        <v>6.060199988910043</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.363810141687033</v>
+        <v>6.51249968946486</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.529013104262233</v>
+        <v>6.701011863828896</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1793</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.76182131103571</v>
+        <v>1.756480478515137</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.903436080528977</v>
+        <v>1.902249294084321</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.62411366398365</v>
+        <v>2.623960273979328</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.977428601213951</v>
+        <v>2.976934108835948</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.164180877454562</v>
+        <v>3.212726797220334</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.62496818093237</v>
+        <v>2.648925589881983</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.042209857360568</v>
+        <v>3.090221536350889</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.575141213573829</v>
+        <v>2.624388775967546</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.235296814998627</v>
+        <v>2.308553924778323</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.500826986878465</v>
+        <v>2.600174312173039</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.574988070670713</v>
+        <v>2.674896106689388</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.334408052362335</v>
+        <v>3.458104673390579</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.583526579974745</v>
+        <v>3.732216127752572</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.697717333380311</v>
+        <v>3.869716092946973</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>1936</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.369195949782359</v>
+        <v>1.363855117261785</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.228145810286108</v>
+        <v>1.226959023841452</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.659820706522815</v>
+        <v>1.659667316518494</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.738392957549195</v>
+        <v>1.737898465171192</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.768285222635313</v>
+        <v>1.816831142401085</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.187560078716686</v>
+        <v>1.211517487666299</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.619378645070348</v>
+        <v>1.667390324060669</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.255615786407574</v>
+        <v>1.304863348801291</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8330633819509146</v>
+        <v>0.9063204917306109</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.809590866612794</v>
+        <v>0.9089381919073674</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.9148070637245098</v>
+        <v>1.014715099743185</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.362408356575699</v>
+        <v>1.486104977603944</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.407133536320138</v>
+        <v>1.555823084097966</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.47791050886071</v>
+        <v>1.649909268427372</v>
       </c>
     </row>
     <row r="20">
@@ -4639,202 +4639,202 @@
         <v>2079</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.126782639187219</v>
+        <v>1.121441806666645</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.934352902856844</v>
+        <v>0.9331661164121883</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.501582480102769</v>
+        <v>1.501429090098448</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.583707575591085</v>
+        <v>1.583213083213082</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.478318455395822</v>
+        <v>1.526864375161594</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.9098916192300379</v>
+        <v>0.933849028179651</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.258081692864309</v>
+        <v>1.306093371854629</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8391130971776164</v>
+        <v>0.8883606595713331</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6338307963546939</v>
+        <v>0.7070879061343902</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6497128658257054</v>
+        <v>0.7490601911202788</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7336119961658056</v>
+        <v>0.8335200321844809</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.200890581421554</v>
+        <v>1.324587202449798</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.165540112908538</v>
+        <v>1.314229660686365</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.006475378334677</v>
+        <v>1.17847413790134</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.5159</t>
+          <t>X &lt; 0.5158</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2221</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.119722479042863</v>
+        <v>1.11438164652229</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.567960911070891</v>
+        <v>0.5667741246262352</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.073684798715668</v>
+        <v>1.073531408711347</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.20390994230403</v>
+        <v>1.203415449926027</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.160892789028232</v>
+        <v>1.209438708794004</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5577715462635098</v>
+        <v>0.5817289552131228</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6531602414773019</v>
+        <v>0.7011719204676226</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3211658885505386</v>
+        <v>0.3704134509442554</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.05498961331217345</v>
+        <v>0.0182674964675229</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.04943790086221611</v>
+        <v>0.04990942443235724</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.02901524102244935</v>
+        <v>0.07089279499622592</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1404372021928495</v>
+        <v>0.2641338232210941</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.08048445783936842</v>
+        <v>0.229174005617196</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.008953237274035075</v>
+        <v>0.1630455222926273</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.549</t>
+          <t>X &lt; 0.5489</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2343</v>
+        <v>2354</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6361458157829958</v>
+        <v>0.5778746387340021</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2067518051268422</v>
+        <v>-0.243881126624899</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.3559472223179725</v>
+        <v>0.3353081270231684</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5519789195530294</v>
+        <v>0.5497945371041766</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3346539188741389</v>
+        <v>0.295376939696169</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2802521060051291</v>
+        <v>-0.2975692227136122</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.341848715576738</v>
+        <v>-0.3775916663412175</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5303560883835203</v>
+        <v>-0.5661970237999085</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8662023902202307</v>
+        <v>-0.9191790020316333</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6703844491587034</v>
+        <v>-0.7446115315590802</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5530950450169527</v>
+        <v>-0.6283377724819914</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4096713276478212</v>
+        <v>-0.5041537604168056</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4220487613697657</v>
+        <v>-0.5359984315799551</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6417981009247171</v>
+        <v>-0.7729493088492134</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.5821</t>
+          <t>X &lt; 0.582</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2442</v>
+        <v>2453</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3669194353321572</v>
+        <v>0.3690447039045779</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4246204610064908</v>
+        <v>-0.4218893157223462</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3847123049366274</v>
+        <v>0.3831029717723311</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.618881814680492</v>
+        <v>0.616466562264371</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2662207928697669</v>
+        <v>0.2307810319620884</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2302169494499609</v>
+        <v>-0.2460973366508981</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4152264728897634</v>
+        <v>-0.4472706985826136</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5741794925855643</v>
+        <v>-0.6063987042404975</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.8989233314137408</v>
+        <v>-0.9466692398928913</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.868093394417194</v>
+        <v>-0.9344414923814099</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.8457220985057248</v>
+        <v>-0.9125939696298602</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.8295848533092069</v>
+        <v>-0.913387540616597</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.8586587594278825</v>
+        <v>-0.9600558654329063</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8967265248672192</v>
+        <v>-1.01449980395153</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2579</v>
+        <v>2590</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.04152530392988041</v>
+        <v>0.04463270066046476</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7922179090092172</v>
+        <v>-0.788139025338765</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2011592226389354</v>
+        <v>-0.2002141340361305</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.06590860703892076</v>
+        <v>0.06593406593405859</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4899920136874485</v>
+        <v>-0.5178040796646215</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7900648545957765</v>
+        <v>-0.8014740697300482</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.124656304722883</v>
+        <v>-1.149472426029227</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.300213297467934</v>
+        <v>-1.325056808083424</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.649953530773288</v>
+        <v>-1.688127668271932</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.549984455822838</v>
+        <v>-1.604689888150233</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.578655304482602</v>
+        <v>-1.633606191208621</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.484344455615116</v>
+        <v>-1.554401093205158</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.766996773116723</v>
+        <v>-1.851314145536719</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.791403146569827</v>
+        <v>-1.890048930621724</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2717</v>
+        <v>2728</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.01392850152391389</v>
+        <v>-0.01102390077169701</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.032373285195838</v>
+        <v>-1.027595479385901</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.344644769350289</v>
+        <v>-0.3431787786058038</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2312358235107297</v>
+        <v>-0.2300427840968382</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7129863404577677</v>
+        <v>-0.7360522100056315</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.056279484555745</v>
+        <v>-1.064834549451291</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.121334453071661</v>
+        <v>-1.142489259543353</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.458560665791772</v>
+        <v>-1.479027296697389</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.793719610622603</v>
+        <v>-1.825688501504807</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.741978500507336</v>
+        <v>-1.788129315322529</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.853180296508853</v>
+        <v>-1.89920027651533</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.945903370815579</v>
+        <v>-2.004306126443531</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.272498424467756</v>
+        <v>-2.342995542892822</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.321191107226539</v>
+        <v>-2.404009686517973</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2855</v>
+        <v>2866</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.168648258754132</v>
+        <v>-0.1655477401353309</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9006127618960562</v>
+        <v>-0.8966245597996121</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5440961182624946</v>
+        <v>-0.5419452160495837</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3601387661610218</v>
+        <v>-0.358533677727003</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7748261860169734</v>
+        <v>-0.7942180850513054</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.261901995106363</v>
+        <v>-1.268108914905632</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.293035952592959</v>
+        <v>-1.310211054404554</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.391915418366807</v>
+        <v>-1.409287529441762</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.783751621227715</v>
+        <v>-1.810700818550892</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.810506173616844</v>
+        <v>-1.849398260996715</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.856267605610235</v>
+        <v>-1.895256555079392</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.977854214404097</v>
+        <v>-2.02737232105784</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.238952997466939</v>
+        <v>-2.299028504368117</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.20431655399841</v>
+        <v>-2.275314068154835</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2992</v>
+        <v>3003</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.09212540168421413</v>
+        <v>-0.08968742170396382</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.530184680189393</v>
+        <v>-0.5277831057310607</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4742194956992023</v>
+        <v>-0.4724283582115589</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3926243807541994</v>
+        <v>-0.3909961594993163</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6130318865376623</v>
+        <v>-0.6299245346153697</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9308972215588014</v>
+        <v>-0.9369409196611045</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8976793825366514</v>
+        <v>-0.9133323359431742</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9131854529861769</v>
+        <v>-0.9292744581634835</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.189637693780455</v>
+        <v>-1.214195597595918</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.153701788056239</v>
+        <v>-1.18869831464621</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.139736321255974</v>
+        <v>-1.175017006292684</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.220546809955714</v>
+        <v>-1.264940112535086</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.388439053165527</v>
+        <v>-1.44210804904683</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.411613069165533</v>
+        <v>-1.474428515001314</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3131</v>
+        <v>3142</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.0238549618320576</v>
+        <v>-0.02199772029109681</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2581854834454589</v>
+        <v>-0.2568906855659847</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3175546031972729</v>
+        <v>-0.3163957534162165</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.07457259271773609</v>
+        <v>-0.07414793328499769</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3407977904720099</v>
+        <v>-0.3557541053623154</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6631898837654475</v>
+        <v>-0.6688445745139546</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5713755859237608</v>
+        <v>-0.5853581544015967</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5430311284476446</v>
+        <v>-0.5575286198630565</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6822638233113523</v>
+        <v>-0.7042748017011533</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.36646393982479</v>
+        <v>-0.3982773198536051</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4257618498704545</v>
+        <v>-0.4575647883121121</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.4373973639203328</v>
+        <v>-0.477099236641223</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6162349447286033</v>
+        <v>-0.663657172434327</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5961733658024144</v>
+        <v>-0.6514556041862676</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3268</v>
+        <v>3279</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.05125072415550136</v>
+        <v>-0.04960149681893711</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3421021235981812</v>
+        <v>-0.3406301437104204</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6289900072858288</v>
+        <v>-0.6268445275368748</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2992963208356301</v>
+        <v>-0.2981583633757552</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4854170145953702</v>
+        <v>-0.4972435796032926</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7208850115465921</v>
+        <v>-0.7251124117370651</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6975414230641519</v>
+        <v>-0.7085169811610754</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.8426843695923623</v>
+        <v>-0.8535199864189025</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.9481802265362589</v>
+        <v>-0.9653261597023288</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5895836974317419</v>
+        <v>-0.6151761411331123</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6856114652465948</v>
+        <v>-0.7110454977558334</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7871417735832793</v>
+        <v>-0.818848284478527</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9150187128323068</v>
+        <v>-0.9532476677665755</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7640273407604568</v>
+        <v>-0.8092504481763996</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3405</v>
+        <v>3416</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.06983403981615055</v>
+        <v>0.07081555919000948</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1559007773880623</v>
+        <v>-0.1551325506496042</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3592388479316782</v>
+        <v>-0.3580511177914474</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2131637381177143</v>
+        <v>-0.2123676090401219</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2962267286397022</v>
+        <v>-0.3062460126933217</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4809509377420227</v>
+        <v>-0.4848214325468803</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5204923014189475</v>
+        <v>-0.5296759485772711</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.7664639701408689</v>
+        <v>-0.7751391628998476</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9288001211149322</v>
+        <v>-0.942388019868865</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6480995202823721</v>
+        <v>-0.6684988580177205</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.7485130775085764</v>
+        <v>-0.7687222544684644</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9326507948553697</v>
+        <v>-0.9576601646425047</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.072326628775002</v>
+        <v>-1.102554933446783</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.9183741236073359</v>
+        <v>-0.9543884457809213</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3544</v>
+        <v>3555</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3821957885429583</v>
+        <v>-0.3800669818376576</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.4925520673552057</v>
+        <v>-0.490821850889489</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6753404563138332</v>
+        <v>-0.6732299269610209</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5862488149618201</v>
+        <v>-0.584351833299948</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6027904368585766</v>
+        <v>-0.60957942794888</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.7405819062434915</v>
+        <v>-0.7425652219084711</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.8664477197529692</v>
+        <v>-0.872331069343538</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.036666834940348</v>
+        <v>-1.042246410041635</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.138755591616309</v>
+        <v>-1.148303893077639</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9024084439055358</v>
+        <v>-0.9173449594096255</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.035173364387255</v>
+        <v>-1.049803689250545</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.239027086922519</v>
+        <v>-1.257277875901089</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.276951835930383</v>
+        <v>-1.299553464907788</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.28954187253585</v>
+        <v>-1.316274432796597</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3681</v>
+        <v>3692</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.5015224812673367</v>
+        <v>-0.4993156035644404</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.7479374878007263</v>
+        <v>-0.7455567286173448</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.8844899763922243</v>
+        <v>-0.8818419132103585</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6313706622452102</v>
+        <v>-0.6294281083584252</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7756967254486256</v>
+        <v>-0.7799234760737122</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8160512831834481</v>
+        <v>-0.8168497225191018</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.9675237051922849</v>
+        <v>-0.9711103652031241</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.17592276651569</v>
+        <v>-1.17905692974999</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.35791050629274</v>
+        <v>-1.363738211215932</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.162007751865069</v>
+        <v>-1.171935479875401</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.270373884041575</v>
+        <v>-1.28005726407212</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.411126176671772</v>
+        <v>-1.423600061167896</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.38184209226835</v>
+        <v>-1.397776869354296</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.331257521745414</v>
+        <v>-1.350491419233236</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3819</v>
+        <v>3830</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3909922867296629</v>
+        <v>-0.3893728189020749</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4768580619954648</v>
+        <v>-0.4753815701157222</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5704244221913441</v>
+        <v>-0.5687764427470228</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3738852412339071</v>
+        <v>-0.3727678571428683</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5584697882889742</v>
+        <v>-0.5614219538124132</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5343289783744112</v>
+        <v>-0.5350447283639213</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.6310458104817016</v>
+        <v>-0.6337413279487976</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.7964017148077787</v>
+        <v>-0.7987397501568196</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7124170980103557</v>
+        <v>-0.7172504673565214</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6325692430323997</v>
+        <v>-0.6400827473184378</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7442751960071092</v>
+        <v>-0.7515227477448221</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.8523935969607663</v>
+        <v>-0.8615675150201554</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.8915553996843641</v>
+        <v>-0.9029678579990232</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.8606982091845552</v>
+        <v>-0.8743932152271086</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3957</v>
+        <v>3968</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3133352241044491</v>
+        <v>-0.3121716088608579</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3758007882492223</v>
+        <v>-0.3746959452187184</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.454615443837092</v>
+        <v>-0.4533500951406495</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4116017300282735</v>
+        <v>-0.4104359692595025</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.6085032229538498</v>
+        <v>-0.6095300418463552</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4992032324877584</v>
+        <v>-0.4991597991953753</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4693580012756868</v>
+        <v>-0.4707405559227027</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4433121065193504</v>
+        <v>-0.4448361441841016</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3895274708198286</v>
+        <v>-0.392542390576196</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3167447277462543</v>
+        <v>-0.3214201844960485</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4568641943103913</v>
+        <v>-0.4611840326027021</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4336484362950301</v>
+        <v>-0.4393639317784164</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4101921854109278</v>
+        <v>-0.417372070915377</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4229603194861582</v>
+        <v>-0.4314107129109317</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.07049640619308661</v>
+        <v>-0.05746490890835787</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.0867454155387648</v>
+        <v>-0.0733714944489634</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1517541707984265</v>
+        <v>-0.1381444882506386</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.05701377280383468</v>
+        <v>-0.06795695191807027</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1434759295564589</v>
+        <v>-0.1550939912887443</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.07648175320230877</v>
+        <v>-0.08782967402421349</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.02274769302518109</v>
+        <v>0.01067906573992872</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.05670441425686334</v>
+        <v>0.06896329432137804</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.05796763512568504</v>
+        <v>0.06974471404667071</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1241913839734039</v>
+        <v>0.1111404731324228</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1040154661300363</v>
+        <v>0.09104872009289977</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1277441092025882</v>
+        <v>0.1142157218080513</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1608057341507134</v>
+        <v>0.1467784688805622</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.156214528073825</v>
+        <v>0.141657388538917</v>
       </c>
     </row>
   </sheetData>
